--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aff3392055fd9681/SEPLAG/2022/SPLOR/DCPPN/LeiOrcamentariaAnual/LOA/bancos/SISOR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\SEPLAG\2022\SPLOR\DCPPN\LeiOrcamentariaAnual\LOA\bancos\SISOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D911647A-F49E-410F-9576-DA5A6B9144D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B68D5B-F6C6-42D8-B5AB-32E509FBDB23}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98CD85CA-BFE1-451F-A64B-00957618F9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="10890"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_QDD_INVESTIMENTO" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -350,10 +337,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -787,7 +771,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -830,13 +814,11 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -879,7 +861,6 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Vírgula" xfId="42" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1183,15 +1164,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -1207,7 +1188,7 @@
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="31.28515625" bestFit="1" customWidth="1"/>
@@ -3915,9 +3896,6 @@
         <v>102</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="N39" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <legacyDrawing r:id="rId1"/>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -1,43 +1,450 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE_QDD_INVESTIMENTO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BASE_QDD_INVESTIMENTO" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+  <si>
+    <t xml:space="preserve">ANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_ORGAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORGAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PODER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_UO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEQ_PROGTRAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUB_FUNCAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENT_PROJATIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJ_ATIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESC_PROJETO_ATIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_NATUREZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATUREZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COD_FONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME_ACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOME_PROGRAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4610 - IMOBILIZAÇÕES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECURSOS PRÓPRIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAÇÃO DE VALOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.580.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBRAS E INSTALAÇÕES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOIO ÀS POLÍTICAS PÚBLICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE SANEAMENTO DE MINAS GERAIS  - COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRENOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OP CRÉD CONTRAT EXTERNA - KFW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.062.500.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.500.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.752.420,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP SISTEMA ADUTOR RIO MANSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.720.630,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCIEDADES CONTROLADAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS CEMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4810 - OUTRAS APLICAÇÕES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUIPAMENTOS E SOFTWARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">670.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTRAS APLICAÇÕES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESENVOLVIMENTO SOCIOECONÔMICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.908.160,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTRAS ENTIDADES - BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL  DO BDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.881.263,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTRAS ORIGENS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.300.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MÓVEIS E UTENSÍLIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.940.203,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">241.821.909,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.805.275,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.096.963,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.600.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.194.360,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">508.846.661,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.487.433.034,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">247.223.810,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.000.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.280.000,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.386.354,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +452,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
@@ -182,10 +512,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -211,15 +537,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -245,6 +568,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -420,142 +744,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>COD_ORGAO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ORGAO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PODER</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>COD_UO</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>UO</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SEQ_PROGTRAB</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>FUNCAO</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SUB_FUNCAO</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>PROGRAMA</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>IDENT_PROJATIV</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>PROJ_ATIV</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>AÇÃO</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>VALOR (R$)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>DESC_PROJETO_ATIV</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>COD_NATUREZA</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>NATUREZA</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>COD_FONTE</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>FONTE</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>NOME_ACAO</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>NOME_PROGRAMA</t>
-        </is>
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>2024</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C2" t="s">
+        <v>23</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -563,10 +835,8 @@
       <c r="E2" t="n">
         <v>5011</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
-        </is>
+      <c r="F2" t="s">
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>10929</v>
@@ -589,60 +859,46 @@
       <c r="M2" t="n">
         <v>3017</v>
       </c>
-      <c r="N2" t="n">
-        <v>1000</v>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
       </c>
       <c r="R2" t="n">
         <v>4614</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S2" t="s">
+        <v>28</v>
       </c>
       <c r="T2" t="n">
         <v>51000</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2024</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C3" t="s">
+        <v>23</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -650,10 +906,8 @@
       <c r="E3" t="n">
         <v>5031</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
-        </is>
+      <c r="F3" t="s">
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>10927</v>
@@ -676,60 +930,46 @@
       <c r="M3" t="n">
         <v>3015</v>
       </c>
-      <c r="N3" t="n">
-        <v>12580000</v>
+      <c r="N3" t="s">
+        <v>32</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>4613</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S3" t="s">
+        <v>34</v>
       </c>
       <c r="T3" t="n">
         <v>51000</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
+      <c r="U3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2024</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C4" t="s">
+        <v>23</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -737,10 +977,8 @@
       <c r="E4" t="n">
         <v>5071</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
-        </is>
+      <c r="F4" t="s">
+        <v>35</v>
       </c>
       <c r="G4" t="n">
         <v>9775</v>
@@ -763,60 +1001,46 @@
       <c r="M4" t="n">
         <v>6010</v>
       </c>
-      <c r="N4" t="n">
-        <v>120000</v>
+      <c r="N4" t="s">
+        <v>36</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>27</v>
       </c>
       <c r="R4" t="n">
         <v>4614</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S4" t="s">
+        <v>28</v>
       </c>
       <c r="T4" t="n">
         <v>51000</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
-        </is>
+      <c r="U4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>2024</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C5" t="s">
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -824,10 +1048,8 @@
       <c r="E5" t="n">
         <v>5081</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F5" t="s">
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>11021</v>
@@ -850,60 +1072,46 @@
       <c r="M5" t="n">
         <v>6009</v>
       </c>
-      <c r="N5" t="n">
-        <v>50000000</v>
+      <c r="N5" t="s">
+        <v>40</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>4614</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S5" t="s">
+        <v>28</v>
       </c>
       <c r="T5" t="n">
         <v>22199</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2024</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C6" t="s">
+        <v>23</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -911,10 +1119,8 @@
       <c r="E6" t="n">
         <v>5081</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F6" t="s">
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>11021</v>
@@ -937,60 +1143,46 @@
       <c r="M6" t="n">
         <v>6009</v>
       </c>
-      <c r="N6" t="n">
-        <v>50000000</v>
+      <c r="N6" t="s">
+        <v>40</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>27</v>
       </c>
       <c r="R6" t="n">
         <v>4614</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S6" t="s">
+        <v>28</v>
       </c>
       <c r="T6" t="n">
         <v>51000</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U6" t="s">
+        <v>29</v>
+      </c>
+      <c r="V6" t="s">
+        <v>41</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>2024</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -998,10 +1190,8 @@
       <c r="E7" t="n">
         <v>5081</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F7" t="s">
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>11022</v>
@@ -1024,60 +1214,46 @@
       <c r="M7" t="n">
         <v>8008</v>
       </c>
-      <c r="N7" t="n">
-        <v>100000000</v>
+      <c r="N7" t="s">
+        <v>44</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>27</v>
       </c>
       <c r="R7" t="n">
         <v>4611</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>TERRENOS</t>
-        </is>
+      <c r="S7" t="s">
+        <v>46</v>
       </c>
       <c r="T7" t="n">
         <v>51000</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U7" t="s">
+        <v>29</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>2024</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -1085,10 +1261,8 @@
       <c r="E8" t="n">
         <v>5081</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F8" t="s">
+        <v>39</v>
       </c>
       <c r="G8" t="n">
         <v>11022</v>
@@ -1111,60 +1285,46 @@
       <c r="M8" t="n">
         <v>8008</v>
       </c>
-      <c r="N8" t="n">
-        <v>250000000</v>
+      <c r="N8" t="s">
+        <v>47</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>27</v>
       </c>
       <c r="R8" t="n">
         <v>4613</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S8" t="s">
+        <v>34</v>
       </c>
       <c r="T8" t="n">
         <v>21204</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U8" t="s">
+        <v>48</v>
+      </c>
+      <c r="V8" t="s">
+        <v>45</v>
+      </c>
+      <c r="W8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>2024</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C9" t="s">
+        <v>23</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -1172,10 +1332,8 @@
       <c r="E9" t="n">
         <v>5081</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F9" t="s">
+        <v>39</v>
       </c>
       <c r="G9" t="n">
         <v>11022</v>
@@ -1198,60 +1356,46 @@
       <c r="M9" t="n">
         <v>8008</v>
       </c>
-      <c r="N9" t="n">
-        <v>1062500000</v>
+      <c r="N9" t="s">
+        <v>49</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>27</v>
       </c>
       <c r="R9" t="n">
         <v>4613</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S9" t="s">
+        <v>34</v>
       </c>
       <c r="T9" t="n">
         <v>22199</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" t="s">
+        <v>45</v>
+      </c>
+      <c r="W9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>2024</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C10" t="s">
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -1259,10 +1403,8 @@
       <c r="E10" t="n">
         <v>5081</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F10" t="s">
+        <v>39</v>
       </c>
       <c r="G10" t="n">
         <v>11022</v>
@@ -1285,60 +1427,46 @@
       <c r="M10" t="n">
         <v>8008</v>
       </c>
-      <c r="N10" t="n">
-        <v>97500000</v>
+      <c r="N10" t="s">
+        <v>50</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>27</v>
       </c>
       <c r="R10" t="n">
         <v>4613</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S10" t="s">
+        <v>34</v>
       </c>
       <c r="T10" t="n">
         <v>51000</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U10" t="s">
+        <v>29</v>
+      </c>
+      <c r="V10" t="s">
+        <v>45</v>
+      </c>
+      <c r="W10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>2024</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -1346,10 +1474,8 @@
       <c r="E11" t="n">
         <v>5081</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F11" t="s">
+        <v>39</v>
       </c>
       <c r="G11" t="n">
         <v>11022</v>
@@ -1372,60 +1498,46 @@
       <c r="M11" t="n">
         <v>8008</v>
       </c>
-      <c r="N11" t="n">
-        <v>40000000</v>
+      <c r="N11" t="s">
+        <v>51</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>27</v>
       </c>
       <c r="R11" t="n">
         <v>4614</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S11" t="s">
+        <v>28</v>
       </c>
       <c r="T11" t="n">
         <v>22199</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" t="s">
+        <v>45</v>
+      </c>
+      <c r="W11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>2024</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -1433,10 +1545,8 @@
       <c r="E12" t="n">
         <v>5081</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
+      <c r="F12" t="s">
+        <v>39</v>
       </c>
       <c r="G12" t="n">
         <v>11023</v>
@@ -1459,60 +1569,46 @@
       <c r="M12" t="n">
         <v>8009</v>
       </c>
-      <c r="N12" t="n">
-        <v>45752420</v>
+      <c r="N12" t="s">
+        <v>52</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P12" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>27</v>
       </c>
       <c r="R12" t="n">
         <v>4613</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S12" t="s">
+        <v>34</v>
       </c>
       <c r="T12" t="n">
         <v>51000</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U12" t="s">
+        <v>29</v>
+      </c>
+      <c r="V12" t="s">
+        <v>53</v>
+      </c>
+      <c r="W12" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>2024</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C13" t="s">
+        <v>23</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -1520,10 +1616,8 @@
       <c r="E13" t="n">
         <v>5121</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
+      <c r="F13" t="s">
+        <v>54</v>
       </c>
       <c r="G13" t="n">
         <v>10542</v>
@@ -1546,60 +1640,46 @@
       <c r="M13" t="n">
         <v>3010</v>
       </c>
-      <c r="N13" t="n">
-        <v>344720630</v>
+      <c r="N13" t="s">
+        <v>55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>57</v>
       </c>
       <c r="R13" t="n">
         <v>4511</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+      <c r="S13" t="s">
+        <v>58</v>
       </c>
       <c r="T13" t="n">
         <v>51000</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS CEMIG</t>
-        </is>
+      <c r="U13" t="s">
+        <v>29</v>
+      </c>
+      <c r="V13" t="s">
+        <v>56</v>
+      </c>
+      <c r="W13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>2024</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C14" t="s">
+        <v>23</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -1607,10 +1687,8 @@
       <c r="E14" t="n">
         <v>5121</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
+      <c r="F14" t="s">
+        <v>54</v>
       </c>
       <c r="G14" t="n">
         <v>9994</v>
@@ -1633,60 +1711,46 @@
       <c r="M14" t="n">
         <v>3011</v>
       </c>
-      <c r="N14" t="n">
-        <v>40000</v>
+      <c r="N14" t="s">
+        <v>60</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P14" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>62</v>
       </c>
       <c r="R14" t="n">
         <v>4817</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+      <c r="S14" t="s">
+        <v>63</v>
       </c>
       <c r="T14" t="n">
         <v>51000</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS CEMIG</t>
-        </is>
+      <c r="U14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V14" t="s">
+        <v>61</v>
+      </c>
+      <c r="W14" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>2024</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C15" t="s">
+        <v>23</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -1694,10 +1758,8 @@
       <c r="E15" t="n">
         <v>5131</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
-        </is>
+      <c r="F15" t="s">
+        <v>64</v>
       </c>
       <c r="G15" t="n">
         <v>9723</v>
@@ -1720,60 +1782,46 @@
       <c r="M15" t="n">
         <v>6008</v>
       </c>
-      <c r="N15" t="n">
-        <v>500000</v>
+      <c r="N15" t="s">
+        <v>65</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>27</v>
       </c>
       <c r="R15" t="n">
         <v>4614</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S15" t="s">
+        <v>28</v>
       </c>
       <c r="T15" t="n">
         <v>51000</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
-        </is>
+      <c r="U15" t="s">
+        <v>29</v>
+      </c>
+      <c r="V15" t="s">
+        <v>66</v>
+      </c>
+      <c r="W15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>2024</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C16" t="s">
+        <v>23</v>
       </c>
       <c r="D16" t="n">
         <v>3</v>
@@ -1781,10 +1829,8 @@
       <c r="E16" t="n">
         <v>5131</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
-        </is>
+      <c r="F16" t="s">
+        <v>64</v>
       </c>
       <c r="G16" t="n">
         <v>9723</v>
@@ -1807,60 +1853,46 @@
       <c r="M16" t="n">
         <v>6008</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
+      <c r="N16" t="s">
+        <v>68</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>62</v>
       </c>
       <c r="R16" t="n">
         <v>4817</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+      <c r="S16" t="s">
+        <v>63</v>
       </c>
       <c r="T16" t="n">
         <v>51000</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
-        </is>
+      <c r="U16" t="s">
+        <v>29</v>
+      </c>
+      <c r="V16" t="s">
+        <v>66</v>
+      </c>
+      <c r="W16" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>2024</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C17" t="s">
+        <v>23</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -1868,10 +1900,8 @@
       <c r="E17" t="n">
         <v>5191</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="F17" t="s">
+        <v>69</v>
       </c>
       <c r="G17" t="n">
         <v>9796</v>
@@ -1894,60 +1924,46 @@
       <c r="M17" t="n">
         <v>6011</v>
       </c>
-      <c r="N17" t="n">
-        <v>670000</v>
+      <c r="N17" t="s">
+        <v>70</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P17" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>62</v>
       </c>
       <c r="R17" t="n">
         <v>4817</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+      <c r="S17" t="s">
+        <v>63</v>
       </c>
       <c r="T17" t="n">
         <v>51000</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
+      <c r="U17" t="s">
+        <v>29</v>
+      </c>
+      <c r="V17" t="s">
+        <v>71</v>
+      </c>
+      <c r="W17" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>2024</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C18" t="s">
+        <v>23</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -1955,10 +1971,8 @@
       <c r="E18" t="n">
         <v>5191</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="F18" t="s">
+        <v>69</v>
       </c>
       <c r="G18" t="n">
         <v>10513</v>
@@ -1981,60 +1995,46 @@
       <c r="M18" t="n">
         <v>6002</v>
       </c>
-      <c r="N18" t="n">
-        <v>1000</v>
+      <c r="N18" t="s">
+        <v>25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P18" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>62</v>
       </c>
       <c r="R18" t="n">
         <v>4819</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="S18" t="s">
+        <v>74</v>
       </c>
       <c r="T18" t="n">
         <v>11101</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
-        </is>
+      <c r="U18" t="s">
+        <v>75</v>
+      </c>
+      <c r="V18" t="s">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>2024</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C19" t="s">
+        <v>23</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -2042,10 +2042,8 @@
       <c r="E19" t="n">
         <v>5191</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="F19" t="s">
+        <v>69</v>
       </c>
       <c r="G19" t="n">
         <v>10513</v>
@@ -2068,60 +2066,46 @@
       <c r="M19" t="n">
         <v>6002</v>
       </c>
-      <c r="N19" t="n">
-        <v>186000</v>
+      <c r="N19" t="s">
+        <v>77</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P19" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>62</v>
       </c>
       <c r="R19" t="n">
         <v>4819</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="S19" t="s">
+        <v>74</v>
       </c>
       <c r="T19" t="n">
         <v>51000</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
-        </is>
+      <c r="U19" t="s">
+        <v>29</v>
+      </c>
+      <c r="V19" t="s">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>2024</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C20" t="s">
+        <v>23</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -2129,10 +2113,8 @@
       <c r="E20" t="n">
         <v>5191</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
+      <c r="F20" t="s">
+        <v>69</v>
       </c>
       <c r="G20" t="n">
         <v>9058</v>
@@ -2155,60 +2137,46 @@
       <c r="M20" t="n">
         <v>6001</v>
       </c>
-      <c r="N20" t="n">
-        <v>1000</v>
+      <c r="N20" t="s">
+        <v>25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
+      <c r="P20" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>57</v>
       </c>
       <c r="R20" t="n">
         <v>4511</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+      <c r="S20" t="s">
+        <v>58</v>
       </c>
       <c r="T20" t="n">
         <v>51000</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
-        </is>
+      <c r="U20" t="s">
+        <v>29</v>
+      </c>
+      <c r="V20" t="s">
+        <v>78</v>
+      </c>
+      <c r="W20" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>2024</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C21" t="s">
+        <v>23</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -2216,10 +2184,8 @@
       <c r="E21" t="n">
         <v>5201</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
+      <c r="F21" t="s">
+        <v>79</v>
       </c>
       <c r="G21" t="n">
         <v>9087</v>
@@ -2242,60 +2208,46 @@
       <c r="M21" t="n">
         <v>6004</v>
       </c>
-      <c r="N21" t="n">
-        <v>23908160</v>
+      <c r="N21" t="s">
+        <v>80</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P21" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>62</v>
       </c>
       <c r="R21" t="n">
         <v>4813</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
-        </is>
+      <c r="S21" t="s">
+        <v>82</v>
       </c>
       <c r="T21" t="n">
         <v>12400</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
-        </is>
+      <c r="U21" t="s">
+        <v>83</v>
+      </c>
+      <c r="V21" t="s">
+        <v>81</v>
+      </c>
+      <c r="W21" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>2024</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C22" t="s">
+        <v>23</v>
       </c>
       <c r="D22" t="n">
         <v>3</v>
@@ -2303,10 +2255,8 @@
       <c r="E22" t="n">
         <v>5201</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
+      <c r="F22" t="s">
+        <v>79</v>
       </c>
       <c r="G22" t="n">
         <v>10991</v>
@@ -2329,60 +2279,46 @@
       <c r="M22" t="n">
         <v>8006</v>
       </c>
-      <c r="N22" t="n">
-        <v>600000000</v>
+      <c r="N22" t="s">
+        <v>85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P22" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>62</v>
       </c>
       <c r="R22" t="n">
         <v>4819</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="S22" t="s">
+        <v>74</v>
       </c>
       <c r="T22" t="n">
         <v>12400</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
-        </is>
+      <c r="U22" t="s">
+        <v>83</v>
+      </c>
+      <c r="V22" t="s">
+        <v>86</v>
+      </c>
+      <c r="W22" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>2024</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C23" t="s">
+        <v>23</v>
       </c>
       <c r="D23" t="n">
         <v>3</v>
@@ -2390,10 +2326,8 @@
       <c r="E23" t="n">
         <v>5251</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
-        </is>
+      <c r="F23" t="s">
+        <v>87</v>
       </c>
       <c r="G23" t="n">
         <v>11027</v>
@@ -2416,60 +2350,46 @@
       <c r="M23" t="n">
         <v>3018</v>
       </c>
-      <c r="N23" t="n">
-        <v>409881263</v>
+      <c r="N23" t="s">
+        <v>88</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P23" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>27</v>
       </c>
       <c r="R23" t="n">
         <v>4614</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S23" t="s">
+        <v>28</v>
       </c>
       <c r="T23" t="n">
         <v>61000</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>OUTRAS ORIGENS</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
-        </is>
+      <c r="U23" t="s">
+        <v>90</v>
+      </c>
+      <c r="V23" t="s">
+        <v>89</v>
+      </c>
+      <c r="W23" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>2024</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C24" t="s">
+        <v>23</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -2477,10 +2397,8 @@
       <c r="E24" t="n">
         <v>5381</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="F24" t="s">
+        <v>91</v>
       </c>
       <c r="G24" t="n">
         <v>9239</v>
@@ -2503,60 +2421,46 @@
       <c r="M24" t="n">
         <v>8002</v>
       </c>
-      <c r="N24" t="n">
-        <v>4300000</v>
+      <c r="N24" t="s">
+        <v>92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P24" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>27</v>
       </c>
       <c r="R24" t="n">
         <v>4614</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S24" t="s">
+        <v>28</v>
       </c>
       <c r="T24" t="n">
         <v>51000</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
+      <c r="U24" t="s">
+        <v>29</v>
+      </c>
+      <c r="V24" t="s">
+        <v>93</v>
+      </c>
+      <c r="W24" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>2024</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C25" t="s">
+        <v>23</v>
       </c>
       <c r="D25" t="n">
         <v>3</v>
@@ -2564,10 +2468,8 @@
       <c r="E25" t="n">
         <v>5381</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="F25" t="s">
+        <v>91</v>
       </c>
       <c r="G25" t="n">
         <v>9239</v>
@@ -2590,60 +2492,46 @@
       <c r="M25" t="n">
         <v>8002</v>
       </c>
-      <c r="N25" t="n">
-        <v>200000</v>
+      <c r="N25" t="s">
+        <v>95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P25" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>27</v>
       </c>
       <c r="R25" t="n">
         <v>4615</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
-        </is>
+      <c r="S25" t="s">
+        <v>96</v>
       </c>
       <c r="T25" t="n">
         <v>51000</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
+      <c r="U25" t="s">
+        <v>29</v>
+      </c>
+      <c r="V25" t="s">
+        <v>93</v>
+      </c>
+      <c r="W25" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>2024</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C26" t="s">
+        <v>23</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -2651,10 +2539,8 @@
       <c r="E26" t="n">
         <v>5381</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="F26" t="s">
+        <v>91</v>
       </c>
       <c r="G26" t="n">
         <v>9239</v>
@@ -2677,60 +2563,46 @@
       <c r="M26" t="n">
         <v>8002</v>
       </c>
-      <c r="N26" t="n">
-        <v>4000000</v>
+      <c r="N26" t="s">
+        <v>97</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P26" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>62</v>
       </c>
       <c r="R26" t="n">
         <v>4817</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+      <c r="S26" t="s">
+        <v>63</v>
       </c>
       <c r="T26" t="n">
         <v>51000</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
+      <c r="U26" t="s">
+        <v>29</v>
+      </c>
+      <c r="V26" t="s">
+        <v>93</v>
+      </c>
+      <c r="W26" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>2024</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C27" t="s">
+        <v>23</v>
       </c>
       <c r="D27" t="n">
         <v>3</v>
@@ -2738,10 +2610,8 @@
       <c r="E27" t="n">
         <v>5381</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
+      <c r="F27" t="s">
+        <v>91</v>
       </c>
       <c r="G27" t="n">
         <v>9239</v>
@@ -2764,60 +2634,46 @@
       <c r="M27" t="n">
         <v>8002</v>
       </c>
-      <c r="N27" t="n">
-        <v>1000</v>
+      <c r="N27" t="s">
+        <v>25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P27" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>62</v>
       </c>
       <c r="R27" t="n">
         <v>4819</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="S27" t="s">
+        <v>74</v>
       </c>
       <c r="T27" t="n">
         <v>11101</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
-        </is>
+      <c r="U27" t="s">
+        <v>75</v>
+      </c>
+      <c r="V27" t="s">
+        <v>93</v>
+      </c>
+      <c r="W27" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>2024</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C28" t="s">
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
@@ -2825,10 +2681,8 @@
       <c r="E28" t="n">
         <v>5391</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F28" t="s">
+        <v>98</v>
       </c>
       <c r="G28" t="n">
         <v>9420</v>
@@ -2851,60 +2705,46 @@
       <c r="M28" t="n">
         <v>3004</v>
       </c>
-      <c r="N28" t="n">
-        <v>198940203</v>
+      <c r="N28" t="s">
+        <v>99</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P28" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>27</v>
       </c>
       <c r="R28" t="n">
         <v>4613</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S28" t="s">
+        <v>34</v>
       </c>
       <c r="T28" t="n">
         <v>51000</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U28" t="s">
+        <v>29</v>
+      </c>
+      <c r="V28" t="s">
+        <v>100</v>
+      </c>
+      <c r="W28" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>2024</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C29" t="s">
+        <v>23</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -2912,10 +2752,8 @@
       <c r="E29" t="n">
         <v>5391</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F29" t="s">
+        <v>98</v>
       </c>
       <c r="G29" t="n">
         <v>9421</v>
@@ -2938,60 +2776,46 @@
       <c r="M29" t="n">
         <v>3005</v>
       </c>
-      <c r="N29" t="n">
-        <v>241821909</v>
+      <c r="N29" t="s">
+        <v>102</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P29" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>27</v>
       </c>
       <c r="R29" t="n">
         <v>4613</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S29" t="s">
+        <v>34</v>
       </c>
       <c r="T29" t="n">
         <v>51000</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U29" t="s">
+        <v>29</v>
+      </c>
+      <c r="V29" t="s">
+        <v>103</v>
+      </c>
+      <c r="W29" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>2024</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C30" t="s">
+        <v>23</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
@@ -2999,10 +2823,8 @@
       <c r="E30" t="n">
         <v>5391</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F30" t="s">
+        <v>98</v>
       </c>
       <c r="G30" t="n">
         <v>9430</v>
@@ -3025,60 +2847,46 @@
       <c r="M30" t="n">
         <v>3006</v>
       </c>
-      <c r="N30" t="n">
-        <v>30805275</v>
+      <c r="N30" t="s">
+        <v>104</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P30" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>27</v>
       </c>
       <c r="R30" t="n">
         <v>4614</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S30" t="s">
+        <v>28</v>
       </c>
       <c r="T30" t="n">
         <v>51000</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U30" t="s">
+        <v>29</v>
+      </c>
+      <c r="V30" t="s">
+        <v>105</v>
+      </c>
+      <c r="W30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>2024</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C31" t="s">
+        <v>23</v>
       </c>
       <c r="D31" t="n">
         <v>3</v>
@@ -3086,10 +2894,8 @@
       <c r="E31" t="n">
         <v>5391</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F31" t="s">
+        <v>98</v>
       </c>
       <c r="G31" t="n">
         <v>10062</v>
@@ -3112,60 +2918,46 @@
       <c r="M31" t="n">
         <v>3001</v>
       </c>
-      <c r="N31" t="n">
-        <v>49096963</v>
+      <c r="N31" t="s">
+        <v>106</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P31" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>27</v>
       </c>
       <c r="R31" t="n">
         <v>4613</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S31" t="s">
+        <v>34</v>
       </c>
       <c r="T31" t="n">
         <v>51000</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U31" t="s">
+        <v>29</v>
+      </c>
+      <c r="V31" t="s">
+        <v>107</v>
+      </c>
+      <c r="W31" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>2024</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C32" t="s">
+        <v>23</v>
       </c>
       <c r="D32" t="n">
         <v>3</v>
@@ -3173,10 +2965,8 @@
       <c r="E32" t="n">
         <v>5391</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F32" t="s">
+        <v>98</v>
       </c>
       <c r="G32" t="n">
         <v>9440</v>
@@ -3199,60 +2989,46 @@
       <c r="M32" t="n">
         <v>3007</v>
       </c>
-      <c r="N32" t="n">
-        <v>130600000</v>
+      <c r="N32" t="s">
+        <v>109</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P32" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>27</v>
       </c>
       <c r="R32" t="n">
         <v>4614</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S32" t="s">
+        <v>28</v>
       </c>
       <c r="T32" t="n">
         <v>51000</v>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U32" t="s">
+        <v>29</v>
+      </c>
+      <c r="V32" t="s">
+        <v>110</v>
+      </c>
+      <c r="W32" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>2024</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C33" t="s">
+        <v>23</v>
       </c>
       <c r="D33" t="n">
         <v>3</v>
@@ -3260,10 +3036,8 @@
       <c r="E33" t="n">
         <v>5391</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F33" t="s">
+        <v>98</v>
       </c>
       <c r="G33" t="n">
         <v>9450</v>
@@ -3286,60 +3060,46 @@
       <c r="M33" t="n">
         <v>3008</v>
       </c>
-      <c r="N33" t="n">
-        <v>13194360</v>
+      <c r="N33" t="s">
+        <v>111</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P33" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>27</v>
       </c>
       <c r="R33" t="n">
         <v>4614</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S33" t="s">
+        <v>28</v>
       </c>
       <c r="T33" t="n">
         <v>51000</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U33" t="s">
+        <v>29</v>
+      </c>
+      <c r="V33" t="s">
+        <v>112</v>
+      </c>
+      <c r="W33" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>2024</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C34" t="s">
+        <v>23</v>
       </c>
       <c r="D34" t="n">
         <v>3</v>
@@ -3347,10 +3107,8 @@
       <c r="E34" t="n">
         <v>5391</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
+      <c r="F34" t="s">
+        <v>98</v>
       </c>
       <c r="G34" t="n">
         <v>10677</v>
@@ -3373,60 +3131,46 @@
       <c r="M34" t="n">
         <v>3014</v>
       </c>
-      <c r="N34" t="n">
-        <v>508846661</v>
+      <c r="N34" t="s">
+        <v>113</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
+      <c r="P34" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>57</v>
       </c>
       <c r="R34" t="n">
         <v>4511</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+      <c r="S34" t="s">
+        <v>58</v>
       </c>
       <c r="T34" t="n">
         <v>51000</v>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U34" t="s">
+        <v>29</v>
+      </c>
+      <c r="V34" t="s">
+        <v>114</v>
+      </c>
+      <c r="W34" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>2024</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C35" t="s">
+        <v>23</v>
       </c>
       <c r="D35" t="n">
         <v>3</v>
@@ -3434,10 +3178,8 @@
       <c r="E35" t="n">
         <v>5401</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
+      <c r="F35" t="s">
+        <v>115</v>
       </c>
       <c r="G35" t="n">
         <v>9332</v>
@@ -3460,60 +3202,46 @@
       <c r="M35" t="n">
         <v>3002</v>
       </c>
-      <c r="N35" t="n">
-        <v>3487433034</v>
+      <c r="N35" t="s">
+        <v>116</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P35" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>4613</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S35" t="s">
+        <v>34</v>
       </c>
       <c r="T35" t="n">
         <v>51000</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U35" t="s">
+        <v>29</v>
+      </c>
+      <c r="V35" t="s">
+        <v>117</v>
+      </c>
+      <c r="W35" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>2024</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C36" t="s">
+        <v>23</v>
       </c>
       <c r="D36" t="n">
         <v>3</v>
@@ -3521,10 +3249,8 @@
       <c r="E36" t="n">
         <v>5401</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
+      <c r="F36" t="s">
+        <v>115</v>
       </c>
       <c r="G36" t="n">
         <v>9408</v>
@@ -3547,60 +3273,46 @@
       <c r="M36" t="n">
         <v>3003</v>
       </c>
-      <c r="N36" t="n">
-        <v>247223810</v>
+      <c r="N36" t="s">
+        <v>119</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P36" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>27</v>
       </c>
       <c r="R36" t="n">
         <v>4614</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S36" t="s">
+        <v>28</v>
       </c>
       <c r="T36" t="n">
         <v>51000</v>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
+      <c r="U36" t="s">
+        <v>29</v>
+      </c>
+      <c r="V36" t="s">
+        <v>120</v>
+      </c>
+      <c r="W36" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>2024</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C37" t="s">
+        <v>23</v>
       </c>
       <c r="D37" t="n">
         <v>3</v>
@@ -3608,10 +3320,8 @@
       <c r="E37" t="n">
         <v>5511</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
+      <c r="F37" t="s">
+        <v>121</v>
       </c>
       <c r="G37" t="n">
         <v>11024</v>
@@ -3634,60 +3344,46 @@
       <c r="M37" t="n">
         <v>6012</v>
       </c>
-      <c r="N37" t="n">
-        <v>2000000</v>
+      <c r="N37" t="s">
+        <v>122</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P37" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>27</v>
       </c>
       <c r="R37" t="n">
         <v>4614</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+      <c r="S37" t="s">
+        <v>28</v>
       </c>
       <c r="T37" t="n">
         <v>51000</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U37" t="s">
+        <v>29</v>
+      </c>
+      <c r="V37" t="s">
+        <v>123</v>
+      </c>
+      <c r="W37" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>2024</v>
       </c>
       <c r="B38" t="n">
         <v>1220</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
+      <c r="C38" t="s">
+        <v>23</v>
       </c>
       <c r="D38" t="n">
         <v>3</v>
@@ -3695,10 +3391,8 @@
       <c r="E38" t="n">
         <v>5511</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
+      <c r="F38" t="s">
+        <v>121</v>
       </c>
       <c r="G38" t="n">
         <v>11026</v>
@@ -3721,60 +3415,46 @@
       <c r="M38" t="n">
         <v>8012</v>
       </c>
-      <c r="N38" t="n">
-        <v>45000000</v>
+      <c r="N38" t="s">
+        <v>124</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P38" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>27</v>
       </c>
       <c r="R38" t="n">
         <v>4613</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S38" t="s">
+        <v>34</v>
       </c>
       <c r="T38" t="n">
         <v>51000</v>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
+      <c r="U38" t="s">
+        <v>29</v>
+      </c>
+      <c r="V38" t="s">
+        <v>125</v>
+      </c>
+      <c r="W38" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>2024</v>
       </c>
       <c r="B39" t="n">
         <v>1300</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
-        </is>
+      <c r="C39" t="s">
+        <v>126</v>
       </c>
       <c r="D39" t="n">
         <v>3</v>
@@ -3782,10 +3462,8 @@
       <c r="E39" t="n">
         <v>5261</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
-        </is>
+      <c r="F39" t="s">
+        <v>127</v>
       </c>
       <c r="G39" t="n">
         <v>9927</v>
@@ -3808,60 +3486,46 @@
       <c r="M39" t="n">
         <v>8011</v>
       </c>
-      <c r="N39" t="n">
-        <v>1000</v>
+      <c r="N39" t="s">
+        <v>25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
+      <c r="P39" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>57</v>
       </c>
       <c r="R39" t="n">
         <v>4511</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+      <c r="S39" t="s">
+        <v>58</v>
       </c>
       <c r="T39" t="n">
         <v>11101</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
-        </is>
+      <c r="U39" t="s">
+        <v>75</v>
+      </c>
+      <c r="V39" t="s">
+        <v>128</v>
+      </c>
+      <c r="W39" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>2024</v>
       </c>
       <c r="B40" t="n">
         <v>1500</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
+      <c r="C40" t="s">
+        <v>129</v>
       </c>
       <c r="D40" t="n">
         <v>3</v>
@@ -3869,10 +3533,8 @@
       <c r="E40" t="n">
         <v>5141</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
+      <c r="F40" t="s">
+        <v>130</v>
       </c>
       <c r="G40" t="n">
         <v>10882</v>
@@ -3895,60 +3557,46 @@
       <c r="M40" t="n">
         <v>6006</v>
       </c>
-      <c r="N40" t="n">
-        <v>3280000</v>
+      <c r="N40" t="s">
+        <v>131</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
+      <c r="P40" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>27</v>
       </c>
       <c r="R40" t="n">
         <v>4613</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+      <c r="S40" t="s">
+        <v>34</v>
       </c>
       <c r="T40" t="n">
         <v>51000</v>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
+      <c r="U40" t="s">
+        <v>29</v>
+      </c>
+      <c r="V40" t="s">
+        <v>132</v>
+      </c>
+      <c r="W40" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>2024</v>
       </c>
       <c r="B41" t="n">
         <v>1500</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
+      <c r="C41" t="s">
+        <v>129</v>
       </c>
       <c r="D41" t="n">
         <v>3</v>
@@ -3956,10 +3604,8 @@
       <c r="E41" t="n">
         <v>5141</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
+      <c r="F41" t="s">
+        <v>130</v>
       </c>
       <c r="G41" t="n">
         <v>9116</v>
@@ -3982,50 +3628,39 @@
       <c r="M41" t="n">
         <v>8001</v>
       </c>
-      <c r="N41" t="n">
-        <v>35386354</v>
+      <c r="N41" t="s">
+        <v>134</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
+      <c r="P41" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>62</v>
       </c>
       <c r="R41" t="n">
         <v>4817</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+      <c r="S41" t="s">
+        <v>63</v>
       </c>
       <c r="T41" t="n">
         <v>51000</v>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
+      <c r="U41" t="s">
+        <v>29</v>
+      </c>
+      <c r="V41" t="s">
+        <v>135</v>
+      </c>
+      <c r="W41" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -534,29 +534,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B2" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>5191</v>
+        <v>5011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9796</v>
+        <v>10929</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -565,39 +565,39 @@
         <v>122</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
-        <v>6011</v>
+        <v>3017</v>
       </c>
       <c r="N2" t="n">
-        <v>90000</v>
+        <v>1000</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -610,81 +610,81 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5191</v>
+        <v>5031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9082</v>
+        <v>10927</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>6003</v>
+        <v>3015</v>
       </c>
       <c r="N3" t="n">
-        <v>15882556</v>
+        <v>12580000</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4819</v>
+        <v>4613</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -697,192 +697,192 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL, À CAPTAÇÃO E À COORDENAÇÃO DA TRANSFERÊNCIA DE RECURSOS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B4" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>5191</v>
+        <v>5071</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9058</v>
+        <v>9775</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>705</v>
       </c>
       <c r="K4" t="n">
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>6001</v>
+        <v>6010</v>
       </c>
       <c r="N4" t="n">
-        <v>1000</v>
+        <v>120000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4511</v>
+        <v>4614</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>1190</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA - SEF</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5191</v>
+        <v>5081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9058</v>
+        <v>11021</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>123</v>
+        <v>512</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>6001</v>
+        <v>6009</v>
       </c>
       <c r="N5" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>4511</v>
+        <v>4614</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -896,56 +896,56 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>5011</v>
+        <v>5081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>10011</v>
+        <v>11021</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="J6" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>3014</v>
+        <v>6009</v>
       </c>
       <c r="N6" t="n">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>4819</v>
+        <v>4614</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -958,18 +958,18 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>MINAS + GERAIS - DIVERSIFICAÇÃO E FORTALECIMENTO DA ECONOMIA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -983,56 +983,56 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>5031</v>
+        <v>5081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9617</v>
+        <v>11022</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>572</v>
+        <v>512</v>
       </c>
       <c r="J7" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>3017</v>
+        <v>8008</v>
       </c>
       <c r="N7" t="n">
-        <v>14119841</v>
+        <v>100000000</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>GESTÃO DE PARTICIPAÇÕES, FUNDOS, CONSÓRCIOS, P&amp;D E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4819</v>
+        <v>4611</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>TERRENOS</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1045,18 +1045,18 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>GESTÃO DE PARTICIPAÇÕES, FUNDOS, CONSÓRCIOS, P&amp;D E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>MINAS + GERAIS - DIVERSIFICAÇÃO E FORTALECIMENTO DA ECONOMIA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9897</v>
+        <v>11022</v>
       </c>
       <c r="H8" t="n">
         <v>17</v>
@@ -1087,19 +1087,19 @@
         <v>512</v>
       </c>
       <c r="J8" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
         <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="N8" t="n">
-        <v>80000000</v>
+        <v>250000000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4611</v>
+        <v>4613</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>TERRENOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>51000</v>
+        <v>21204</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1137,13 +1137,13 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9897</v>
+        <v>11022</v>
       </c>
       <c r="H9" t="n">
         <v>17</v>
@@ -1174,19 +1174,19 @@
         <v>512</v>
       </c>
       <c r="J9" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
         <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="N9" t="n">
-        <v>250000000</v>
+        <v>1062500000</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1210,11 +1210,11 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>21204</v>
+        <v>22199</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1224,13 +1224,13 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9897</v>
+        <v>11022</v>
       </c>
       <c r="H10" t="n">
         <v>17</v>
@@ -1261,19 +1261,19 @@
         <v>512</v>
       </c>
       <c r="J10" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="N10" t="n">
-        <v>885250000</v>
+        <v>97500000</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1311,13 +1311,13 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9897</v>
+        <v>11022</v>
       </c>
       <c r="H11" t="n">
         <v>17</v>
@@ -1348,19 +1348,19 @@
         <v>512</v>
       </c>
       <c r="J11" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>8004</v>
+        <v>8008</v>
       </c>
       <c r="N11" t="n">
-        <v>74750000</v>
+        <v>40000000</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1376,19 +1376,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1398,13 +1398,13 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9897</v>
+        <v>11023</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -1435,26 +1435,26 @@
         <v>512</v>
       </c>
       <c r="J12" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>8004</v>
+        <v>8009</v>
       </c>
       <c r="N12" t="n">
-        <v>40000000</v>
+        <v>45752420</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1463,35 +1463,35 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1505,56 +1505,56 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>9898</v>
+        <v>10542</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I13" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J13" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>8005</v>
+        <v>3010</v>
       </c>
       <c r="N13" t="n">
-        <v>49915500</v>
+        <v>344720630</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PPP - SISTEMA ADUTOR RIO MANSO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4613</v>
+        <v>4511</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1567,18 +1567,18 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>PPP - SISTEMA ADUTOR RIO MANSO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1592,80 +1592,80 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9901</v>
+        <v>9994</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I14" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J14" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>8008</v>
+        <v>3011</v>
       </c>
       <c r="N14" t="n">
-        <v>31000000</v>
+        <v>40000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4614</v>
+        <v>4817</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1679,43 +1679,43 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>5081</v>
+        <v>5131</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9901</v>
+        <v>9723</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I15" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="J15" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>8008</v>
+        <v>6008</v>
       </c>
       <c r="N15" t="n">
-        <v>50000000</v>
+        <v>500000</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1741,18 +1741,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1766,56 +1766,56 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5121</v>
+        <v>5131</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9994</v>
+        <v>9723</v>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J16" t="n">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>3011</v>
+        <v>6008</v>
       </c>
       <c r="N16" t="n">
-        <v>30608</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4614</v>
+        <v>4817</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1853,80 +1853,80 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>5121</v>
+        <v>5191</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9995</v>
+        <v>9796</v>
       </c>
       <c r="H17" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>3012</v>
+        <v>6011</v>
       </c>
       <c r="N17" t="n">
-        <v>629198369</v>
+        <v>670000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4512</v>
+        <v>4817</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>SOCIEDADES COLIGADAS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>12100</v>
+        <v>51000</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - CEMIG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1940,80 +1940,80 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>5131</v>
+        <v>5191</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO INTEGRADO DE MINAS GERAIS - INDI</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9723</v>
+        <v>10513</v>
       </c>
       <c r="H18" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>122</v>
       </c>
       <c r="J18" t="n">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>6008</v>
+        <v>6002</v>
       </c>
       <c r="N18" t="n">
-        <v>500000</v>
+        <v>1000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO INDI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4614</v>
+        <v>4819</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO INDI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -2027,43 +2027,43 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9087</v>
+        <v>10513</v>
       </c>
       <c r="H19" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>122</v>
       </c>
       <c r="J19" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="N19" t="n">
-        <v>21267000</v>
+        <v>186000</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2072,35 +2072,35 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4813</v>
+        <v>4819</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -2114,80 +2114,80 @@
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5251</v>
+        <v>5191</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9629</v>
+        <v>9058</v>
       </c>
       <c r="H20" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>451</v>
+        <v>123</v>
       </c>
       <c r="J20" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>8003</v>
+        <v>6001</v>
       </c>
       <c r="N20" t="n">
-        <v>244358023</v>
+        <v>1000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4613</v>
+        <v>4511</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>12900</v>
+        <v>51000</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>#VEMPRAMINAS - ATRAÇÃO DE INVESTIMENTOS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -2201,80 +2201,80 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>5391</v>
+        <v>5201</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>9420</v>
+        <v>9087</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J21" t="n">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>3004</v>
+        <v>6004</v>
       </c>
       <c r="N21" t="n">
-        <v>308709015</v>
+        <v>23908160</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4613</v>
+        <v>4813</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -2288,80 +2288,80 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5391</v>
+        <v>5201</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>9421</v>
+        <v>10991</v>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I22" t="n">
-        <v>752</v>
+        <v>694</v>
       </c>
       <c r="J22" t="n">
-        <v>92</v>
+        <v>171</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>3005</v>
+        <v>8006</v>
       </c>
       <c r="N22" t="n">
-        <v>120452442</v>
+        <v>600000000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4613</v>
+        <v>4819</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2375,43 +2375,43 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5391</v>
+        <v>5251</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>9430</v>
+        <v>11027</v>
       </c>
       <c r="H23" t="n">
         <v>25</v>
       </c>
       <c r="I23" t="n">
-        <v>752</v>
+        <v>121</v>
       </c>
       <c r="J23" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M23" t="n">
-        <v>3006</v>
+        <v>3018</v>
       </c>
       <c r="N23" t="n">
-        <v>4693805</v>
+        <v>409881263</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2428,27 +2428,27 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>51000</v>
+        <v>61000</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ORIGENS</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2462,43 +2462,43 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>10062</v>
+        <v>9239</v>
       </c>
       <c r="H24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J24" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3001</v>
+        <v>8002</v>
       </c>
       <c r="N24" t="n">
-        <v>1880000000</v>
+        <v>4300000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2524,18 +2524,18 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2549,43 +2549,43 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9440</v>
+        <v>9239</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J25" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3007</v>
+        <v>8002</v>
       </c>
       <c r="N25" t="n">
-        <v>17888000</v>
+        <v>200000</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2594,11 +2594,11 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4614</v>
+        <v>4615</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2611,18 +2611,18 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2636,56 +2636,56 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9450</v>
+        <v>9239</v>
       </c>
       <c r="H26" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J26" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3008</v>
+        <v>8002</v>
       </c>
       <c r="N26" t="n">
-        <v>15165514</v>
+        <v>4000000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4614</v>
+        <v>4817</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2698,18 +2698,18 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2723,80 +2723,80 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>10161</v>
+        <v>9239</v>
       </c>
       <c r="H27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J27" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3009</v>
+        <v>8002</v>
       </c>
       <c r="N27" t="n">
-        <v>12241405</v>
+        <v>1000</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4511</v>
+        <v>4819</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>12100</v>
+        <v>11101</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - CEMIG</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL - PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2810,15 +2810,15 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9332</v>
+        <v>9420</v>
       </c>
       <c r="H28" t="n">
         <v>25</v>
@@ -2827,26 +2827,26 @@
         <v>752</v>
       </c>
       <c r="J28" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="N28" t="n">
-        <v>2901796000</v>
+        <v>198940203</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2872,18 +2872,18 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2897,15 +2897,15 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9408</v>
+        <v>9421</v>
       </c>
       <c r="H29" t="n">
         <v>25</v>
@@ -2914,26 +2914,26 @@
         <v>752</v>
       </c>
       <c r="J29" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>3003</v>
+        <v>3005</v>
       </c>
       <c r="N29" t="n">
-        <v>162092993</v>
+        <v>241821909</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -2959,18 +2959,18 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2984,43 +2984,43 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9899</v>
+        <v>9430</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I30" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J30" t="n">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>8006</v>
+        <v>3006</v>
       </c>
       <c r="N30" t="n">
-        <v>45000000</v>
+        <v>30805275</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3029,11 +3029,11 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3046,18 +3046,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -3071,43 +3071,43 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9900</v>
+        <v>10062</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I31" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J31" t="n">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>8007</v>
+        <v>3001</v>
       </c>
       <c r="N31" t="n">
-        <v>2000000</v>
+        <v>49096963</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3133,155 +3133,155 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>GESTÃO AMBIENTAL E SANEAMENTO</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B32" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>5261</v>
+        <v>5391</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9927</v>
+        <v>9440</v>
       </c>
       <c r="H32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I32" t="n">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="J32" t="n">
-        <v>705</v>
+        <v>94</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M32" t="n">
-        <v>8011</v>
+        <v>3007</v>
       </c>
       <c r="N32" t="n">
-        <v>1000</v>
+        <v>130600000</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>4511</v>
+        <v>4614</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B33" t="n">
-        <v>1480</v>
+        <v>1220</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL - SEDESE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>5071</v>
+        <v>5391</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9775</v>
+        <v>9450</v>
       </c>
       <c r="H33" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J33" t="n">
-        <v>705</v>
+        <v>94</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>6010</v>
+        <v>3008</v>
       </c>
       <c r="N33" t="n">
-        <v>120000</v>
+        <v>13194360</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3307,81 +3307,81 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B34" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5141</v>
+        <v>5391</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9116</v>
+        <v>10677</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I34" t="n">
-        <v>126</v>
+        <v>752</v>
       </c>
       <c r="J34" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="K34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M34" t="n">
-        <v>8001</v>
+        <v>3014</v>
       </c>
       <c r="N34" t="n">
-        <v>45914908</v>
+        <v>508846661</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>4817</v>
+        <v>4511</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3394,68 +3394,68 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B35" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>5381</v>
+        <v>5401</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9239</v>
+        <v>9332</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I35" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J35" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>8002</v>
+        <v>3002</v>
       </c>
       <c r="N35" t="n">
-        <v>3300000</v>
+        <v>3487433034</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3464,11 +3464,11 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3481,68 +3481,68 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B36" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>5381</v>
+        <v>5401</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9239</v>
+        <v>9408</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I36" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J36" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>8002</v>
+        <v>3003</v>
       </c>
       <c r="N36" t="n">
-        <v>200000</v>
+        <v>247223810</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3551,11 +3551,11 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>4615</v>
+        <v>4614</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3568,81 +3568,81 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B37" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5381</v>
+        <v>5511</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>9239</v>
+        <v>11024</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="J37" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
-        <v>8002</v>
+        <v>6012</v>
       </c>
       <c r="N37" t="n">
-        <v>4500000</v>
+        <v>2000000</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -3655,99 +3655,360 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B38" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>5381</v>
+        <v>5511</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9239</v>
+        <v>11026</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I38" t="n">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="J38" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="K38" t="n">
         <v>8</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>8002</v>
+        <v>8012</v>
       </c>
       <c r="N38" t="n">
-        <v>1000</v>
+        <v>45000000</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>4613</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5261</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>9927</v>
+      </c>
+      <c r="H39" t="n">
+        <v>26</v>
+      </c>
+      <c r="I39" t="n">
+        <v>783</v>
+      </c>
+      <c r="J39" t="n">
+        <v>705</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8011</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>4511</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>11101</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>10882</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>126</v>
+      </c>
+      <c r="J40" t="n">
+        <v>30</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" t="n">
+        <v>6006</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>4613</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>9116</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="n">
+        <v>126</v>
+      </c>
+      <c r="J41" t="n">
+        <v>30</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8001</v>
+      </c>
+      <c r="N41" t="n">
+        <v>35386354</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
           <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="T38" t="n">
-        <v>11101</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+      <c r="R41" t="n">
+        <v>4817</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INDI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -1766,43 +1766,43 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5131</v>
+        <v>5191</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9723</v>
+        <v>9796</v>
       </c>
       <c r="H16" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>122</v>
       </c>
       <c r="J16" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>670000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9796</v>
+        <v>10513</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -1870,26 +1870,26 @@
         <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>6011</v>
+        <v>6002</v>
       </c>
       <c r="N17" t="n">
-        <v>670000</v>
+        <v>1000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1898,29 +1898,29 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4817</v>
+        <v>4819</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
         <v>6002</v>
       </c>
       <c r="N18" t="n">
-        <v>1000</v>
+        <v>186000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1993,11 +1993,11 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2035,48 +2035,48 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>10513</v>
+        <v>9058</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="N19" t="n">
-        <v>186000</v>
+        <v>1000</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4819</v>
+        <v>4511</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
@@ -2114,74 +2114,74 @@
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5191</v>
+        <v>5201</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9058</v>
+        <v>9087</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="N20" t="n">
-        <v>1000</v>
+        <v>23908160</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4511</v>
+        <v>4813</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
     </row>
@@ -2209,35 +2209,35 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>9087</v>
+        <v>10991</v>
       </c>
       <c r="H21" t="n">
         <v>23</v>
       </c>
       <c r="I21" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="K21" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" t="n">
         <v>6</v>
       </c>
-      <c r="L21" t="n">
-        <v>4</v>
-      </c>
       <c r="M21" t="n">
-        <v>6004</v>
+        <v>8006</v>
       </c>
       <c r="N21" t="n">
-        <v>23908160</v>
+        <v>600000000</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2246,11 +2246,11 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4813</v>
+        <v>4819</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
     </row>
@@ -2288,74 +2288,74 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5201</v>
+        <v>5251</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>10991</v>
+        <v>11027</v>
       </c>
       <c r="H22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I22" t="n">
-        <v>694</v>
+        <v>121</v>
       </c>
       <c r="J22" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>8006</v>
+        <v>3018</v>
       </c>
       <c r="N22" t="n">
-        <v>600000000</v>
+        <v>409881263</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4819</v>
+        <v>4614</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>12400</v>
+        <v>61000</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>OUTRAS ORIGENS</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
@@ -2375,43 +2375,43 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5251</v>
+        <v>5381</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>11027</v>
+        <v>9239</v>
       </c>
       <c r="H23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J23" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3018</v>
+        <v>8002</v>
       </c>
       <c r="N23" t="n">
-        <v>409881263</v>
+        <v>4300000</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2428,21 +2428,21 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>61000</v>
+        <v>51000</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>OUTRAS ORIGENS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
         <v>8002</v>
       </c>
       <c r="N24" t="n">
-        <v>4300000</v>
+        <v>200000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4614</v>
+        <v>4615</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2578,7 +2578,7 @@
         <v>8002</v>
       </c>
       <c r="N25" t="n">
-        <v>200000</v>
+        <v>4000000</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2590,15 +2590,15 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4615</v>
+        <v>4817</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2665,7 +2665,7 @@
         <v>8002</v>
       </c>
       <c r="N26" t="n">
-        <v>4000000</v>
+        <v>1000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2681,19 +2681,19 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4817</v>
+        <v>4819</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2723,74 +2723,74 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9239</v>
+        <v>9420</v>
       </c>
       <c r="H27" t="n">
+        <v>25</v>
+      </c>
+      <c r="I27" t="n">
+        <v>752</v>
+      </c>
+      <c r="J27" t="n">
+        <v>92</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" t="n">
         <v>4</v>
       </c>
-      <c r="I27" t="n">
-        <v>122</v>
-      </c>
-      <c r="J27" t="n">
-        <v>57</v>
-      </c>
-      <c r="K27" t="n">
-        <v>8</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
       <c r="M27" t="n">
-        <v>8002</v>
+        <v>3004</v>
       </c>
       <c r="N27" t="n">
-        <v>1000</v>
+        <v>198940203</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4819</v>
+        <v>4613</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T27" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9420</v>
+        <v>9421</v>
       </c>
       <c r="H28" t="n">
         <v>25</v>
@@ -2833,20 +2833,20 @@
         <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="N28" t="n">
-        <v>198940203</v>
+        <v>241821909</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9421</v>
+        <v>9430</v>
       </c>
       <c r="H29" t="n">
         <v>25</v>
@@ -2920,20 +2920,20 @@
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="N29" t="n">
-        <v>241821909</v>
+        <v>30805275</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9430</v>
+        <v>10062</v>
       </c>
       <c r="H30" t="n">
         <v>25</v>
@@ -3001,26 +3001,26 @@
         <v>752</v>
       </c>
       <c r="J30" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>3006</v>
+        <v>3001</v>
       </c>
       <c r="N30" t="n">
-        <v>30805275</v>
+        <v>49096963</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3029,11 +3029,11 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10062</v>
+        <v>9440</v>
       </c>
       <c r="H31" t="n">
         <v>25</v>
@@ -3094,20 +3094,20 @@
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="N31" t="n">
-        <v>49096963</v>
+        <v>130600000</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3116,11 +3116,11 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9440</v>
+        <v>9450</v>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -3181,20 +3181,20 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M32" t="n">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="N32" t="n">
-        <v>130600000</v>
+        <v>13194360</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9450</v>
+        <v>10677</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -3268,33 +3268,33 @@
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M33" t="n">
-        <v>3008</v>
+        <v>3014</v>
       </c>
       <c r="N33" t="n">
-        <v>13194360</v>
+        <v>508846661</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>4614</v>
+        <v>4511</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3332,15 +3332,15 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5391</v>
+        <v>5401</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>10677</v>
+        <v>9332</v>
       </c>
       <c r="H34" t="n">
         <v>25</v>
@@ -3349,39 +3349,39 @@
         <v>752</v>
       </c>
       <c r="J34" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3014</v>
+        <v>3002</v>
       </c>
       <c r="N34" t="n">
-        <v>508846661</v>
+        <v>3487433034</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R34" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9332</v>
+        <v>9408</v>
       </c>
       <c r="H35" t="n">
         <v>25</v>
@@ -3442,20 +3442,20 @@
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="N35" t="n">
-        <v>3487433034</v>
+        <v>247223810</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3464,11 +3464,11 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -3506,43 +3506,43 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>5401</v>
+        <v>5511</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9408</v>
+        <v>11024</v>
       </c>
       <c r="H36" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I36" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="J36" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M36" t="n">
-        <v>3003</v>
+        <v>6012</v>
       </c>
       <c r="N36" t="n">
-        <v>247223810</v>
+        <v>2000000</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11024</v>
+        <v>11026</v>
       </c>
       <c r="H37" t="n">
         <v>17</v>
@@ -3613,23 +3613,23 @@
         <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L37" t="n">
         <v>12</v>
       </c>
       <c r="M37" t="n">
-        <v>6012</v>
+        <v>8012</v>
       </c>
       <c r="N37" t="n">
-        <v>2000000</v>
+        <v>45000000</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3638,11 +3638,11 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -3669,85 +3669,85 @@
         <v>2024</v>
       </c>
       <c r="B38" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>5511</v>
+        <v>5261</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>11026</v>
+        <v>9927</v>
       </c>
       <c r="H38" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I38" t="n">
-        <v>512</v>
+        <v>783</v>
       </c>
       <c r="J38" t="n">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="K38" t="n">
         <v>8</v>
       </c>
       <c r="L38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M38" t="n">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="N38" t="n">
-        <v>45000000</v>
+        <v>1000</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4613</v>
+        <v>4511</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T38" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
@@ -3756,85 +3756,85 @@
         <v>2024</v>
       </c>
       <c r="B39" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>5261</v>
+        <v>5141</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>9927</v>
+        <v>10882</v>
       </c>
       <c r="H39" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>783</v>
+        <v>126</v>
       </c>
       <c r="J39" t="n">
-        <v>705</v>
+        <v>30</v>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>8011</v>
+        <v>6006</v>
       </c>
       <c r="N39" t="n">
-        <v>1000</v>
+        <v>3280000</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T39" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>10882</v>
+        <v>9116</v>
       </c>
       <c r="H40" t="n">
         <v>4</v>
@@ -3874,36 +3874,36 @@
         <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>6006</v>
+        <v>8001</v>
       </c>
       <c r="N40" t="n">
-        <v>3280000</v>
+        <v>35386354</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>4613</v>
+        <v>4817</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -3916,97 +3916,10 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5141</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>9116</v>
-      </c>
-      <c r="H41" t="n">
-        <v>4</v>
-      </c>
-      <c r="I41" t="n">
-        <v>126</v>
-      </c>
-      <c r="J41" t="n">
-        <v>30</v>
-      </c>
-      <c r="K41" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>8001</v>
-      </c>
-      <c r="N41" t="n">
-        <v>35386354</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
-        <v>4817</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
-      </c>
-      <c r="T41" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
         <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -2333,11 +2333,11 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T22" t="n">

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMG</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -664,7 +664,7 @@
         <v>3015</v>
       </c>
       <c r="N3" t="n">
-        <v>12580000</v>
+        <v>6380000</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -722,43 +722,43 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>5071</v>
+        <v>5031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9775</v>
+        <v>10927</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="J4" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
-        <v>6010</v>
+        <v>3015</v>
       </c>
       <c r="N4" t="n">
-        <v>120000</v>
+        <v>6240000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -784,18 +784,18 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -809,43 +809,43 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5081</v>
+        <v>5071</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
+          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>11021</v>
+        <v>9775</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="N5" t="n">
-        <v>50000000</v>
+        <v>120000</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -862,27 +862,27 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -969,7 +969,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>11022</v>
+        <v>11021</v>
       </c>
       <c r="H7" t="n">
         <v>17</v>
@@ -1003,23 +1003,23 @@
         <v>21</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>8008</v>
+        <v>6009</v>
       </c>
       <c r="N7" t="n">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>4611</v>
+        <v>4614</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>TERRENOS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1056,7 +1056,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -1099,7 +1099,7 @@
         <v>8008</v>
       </c>
       <c r="N8" t="n">
-        <v>250000000</v>
+        <v>100000000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4613</v>
+        <v>4611</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>TERRENOS</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1186,7 +1186,7 @@
         <v>8008</v>
       </c>
       <c r="N9" t="n">
-        <v>1062500000</v>
+        <v>350000000</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1210,11 +1210,11 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>22199</v>
+        <v>21204</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1273,7 +1273,7 @@
         <v>8008</v>
       </c>
       <c r="N10" t="n">
-        <v>97500000</v>
+        <v>983250000</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1360,7 +1360,7 @@
         <v>8008</v>
       </c>
       <c r="N11" t="n">
-        <v>40000000</v>
+        <v>54750000</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1376,19 +1376,19 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1404,7 +1404,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11023</v>
+        <v>11022</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -1441,20 +1441,20 @@
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="N12" t="n">
-        <v>45752420</v>
+        <v>40000000</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1463,24 +1463,24 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1505,56 +1505,56 @@
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>5121</v>
+        <v>5081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10542</v>
+        <v>11023</v>
       </c>
       <c r="H13" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M13" t="n">
-        <v>3010</v>
+        <v>8009</v>
       </c>
       <c r="N13" t="n">
-        <v>344720630</v>
+        <v>48428689</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1567,18 +1567,18 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9994</v>
+        <v>10542</v>
       </c>
       <c r="H14" t="n">
         <v>25</v>
@@ -1615,33 +1615,33 @@
         <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="N14" t="n">
-        <v>40000</v>
+        <v>259985809</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4817</v>
+        <v>4511</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1665,7 +1665,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1679,43 +1679,43 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9723</v>
+        <v>9994</v>
       </c>
       <c r="H15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I15" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J15" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="N15" t="n">
-        <v>500000</v>
+        <v>4440000</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1741,18 +1741,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1766,56 +1766,56 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5191</v>
+        <v>5131</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9796</v>
+        <v>9723</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
         <v>122</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="N16" t="n">
-        <v>670000</v>
+        <v>500000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>10513</v>
+        <v>9796</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -1870,26 +1870,26 @@
         <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>6002</v>
+        <v>6011</v>
       </c>
       <c r="N17" t="n">
-        <v>1000</v>
+        <v>243000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1898,35 +1898,35 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4819</v>
+        <v>4817</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10513</v>
+        <v>11036</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -1957,19 +1957,19 @@
         <v>122</v>
       </c>
       <c r="J18" t="n">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="N18" t="n">
-        <v>186000</v>
+        <v>1000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1993,11 +1993,11 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2007,13 +2007,13 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>DESENVOLVIMENTO SOCIOECONÔMICO</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -2035,48 +2035,48 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9058</v>
+        <v>11036</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="N19" t="n">
-        <v>1000</v>
+        <v>9256395</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4511</v>
+        <v>4819</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2089,18 +2089,18 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -2114,80 +2114,80 @@
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9087</v>
+        <v>9058</v>
       </c>
       <c r="H20" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="N20" t="n">
-        <v>23908160</v>
+        <v>1000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4813</v>
+        <v>4511</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>12400</v>
+        <v>11101</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -2201,80 +2201,80 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10991</v>
+        <v>9058</v>
       </c>
       <c r="H21" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>694</v>
+        <v>123</v>
       </c>
       <c r="J21" t="n">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>8006</v>
+        <v>6001</v>
       </c>
       <c r="N21" t="n">
-        <v>600000000</v>
+        <v>1000</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4819</v>
+        <v>4511</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -2288,80 +2288,80 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11027</v>
+        <v>9087</v>
       </c>
       <c r="H22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I22" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J22" t="n">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>3018</v>
+        <v>6004</v>
       </c>
       <c r="N22" t="n">
-        <v>409881263</v>
+        <v>26253389</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4613</v>
+        <v>4813</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>61000</v>
+        <v>12400</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>OUTRAS ORIGENS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2375,80 +2375,80 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>9239</v>
+        <v>11046</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="J23" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
         <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>8002</v>
+        <v>8003</v>
       </c>
       <c r="N23" t="n">
-        <v>4300000</v>
+        <v>250000000</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4614</v>
+        <v>4819</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2462,80 +2462,80 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9239</v>
+        <v>10991</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I24" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="J24" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="K24" t="n">
         <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="N24" t="n">
-        <v>200000</v>
+        <v>600000000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4615</v>
+        <v>4819</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2549,80 +2549,80 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5381</v>
+        <v>5251</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9239</v>
+        <v>11027</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J25" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M25" t="n">
-        <v>8002</v>
+        <v>3018</v>
       </c>
       <c r="N25" t="n">
-        <v>4000000</v>
+        <v>285487805</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4817</v>
+        <v>4613</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>51000</v>
+        <v>61000</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ORIGENS</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2665,7 +2665,7 @@
         <v>8002</v>
       </c>
       <c r="N26" t="n">
-        <v>1000</v>
+        <v>5450000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2677,23 +2677,23 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4819</v>
+        <v>4614</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2709,7 +2709,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2723,43 +2723,43 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9420</v>
+        <v>9239</v>
       </c>
       <c r="H27" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J27" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="N27" t="n">
-        <v>198940203</v>
+        <v>400000</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2768,11 +2768,11 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4613</v>
+        <v>4615</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -2785,18 +2785,18 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2810,56 +2810,56 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9421</v>
+        <v>9239</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J28" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3005</v>
+        <v>8002</v>
       </c>
       <c r="N28" t="n">
-        <v>241821909</v>
+        <v>4000000</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>4613</v>
+        <v>4817</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -2872,18 +2872,18 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2897,80 +2897,80 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9430</v>
+        <v>9239</v>
       </c>
       <c r="H29" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J29" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>3006</v>
+        <v>8002</v>
       </c>
       <c r="N29" t="n">
-        <v>30805275</v>
+        <v>1000</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4614</v>
+        <v>4819</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>10062</v>
+        <v>9420</v>
       </c>
       <c r="H30" t="n">
         <v>25</v>
@@ -3001,26 +3001,26 @@
         <v>752</v>
       </c>
       <c r="J30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>3001</v>
+        <v>3004</v>
       </c>
       <c r="N30" t="n">
-        <v>49096963</v>
+        <v>231539977</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3046,18 +3046,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9440</v>
+        <v>9421</v>
       </c>
       <c r="H31" t="n">
         <v>25</v>
@@ -3088,26 +3088,26 @@
         <v>752</v>
       </c>
       <c r="J31" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="N31" t="n">
-        <v>130600000</v>
+        <v>216613767</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3116,11 +3116,11 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3133,18 +3133,18 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9450</v>
+        <v>9430</v>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -3175,26 +3175,26 @@
         <v>752</v>
       </c>
       <c r="J32" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="N32" t="n">
-        <v>13194360</v>
+        <v>42479000</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3220,18 +3220,18 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>10677</v>
+        <v>11134</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -3262,26 +3262,26 @@
         <v>752</v>
       </c>
       <c r="J33" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M33" t="n">
-        <v>3014</v>
+        <v>3009</v>
       </c>
       <c r="N33" t="n">
-        <v>508846661</v>
+        <v>92271447</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3307,18 +3307,18 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
@@ -3332,15 +3332,15 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9332</v>
+        <v>10062</v>
       </c>
       <c r="H34" t="n">
         <v>25</v>
@@ -3349,26 +3349,26 @@
         <v>752</v>
       </c>
       <c r="J34" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="N34" t="n">
-        <v>3487433034</v>
+        <v>100000</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
@@ -3419,15 +3419,15 @@
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9408</v>
+        <v>9440</v>
       </c>
       <c r="H35" t="n">
         <v>25</v>
@@ -3436,26 +3436,26 @@
         <v>752</v>
       </c>
       <c r="J35" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M35" t="n">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="N35" t="n">
-        <v>247223810</v>
+        <v>96218712</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3481,18 +3481,18 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
@@ -3506,43 +3506,43 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>11024</v>
+        <v>9450</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I36" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J36" t="n">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M36" t="n">
-        <v>6012</v>
+        <v>3008</v>
       </c>
       <c r="N36" t="n">
-        <v>2000000</v>
+        <v>18091000</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3568,18 +3568,18 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
@@ -3593,56 +3593,56 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5511</v>
+        <v>5391</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11026</v>
+        <v>10677</v>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I37" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M37" t="n">
-        <v>8012</v>
+        <v>3014</v>
       </c>
       <c r="N37" t="n">
-        <v>45000000</v>
+        <v>190392082</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>4613</v>
+        <v>4511</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -3655,155 +3655,155 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B38" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>5261</v>
+        <v>5401</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9927</v>
+        <v>9332</v>
       </c>
       <c r="H38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I38" t="n">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="J38" t="n">
-        <v>705</v>
+        <v>72</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>8011</v>
+        <v>3002</v>
       </c>
       <c r="N38" t="n">
-        <v>1000</v>
+        <v>4721877188</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T38" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B39" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>5141</v>
+        <v>5401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>10882</v>
+        <v>9408</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>126</v>
+        <v>752</v>
       </c>
       <c r="J39" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>6006</v>
+        <v>3003</v>
       </c>
       <c r="N39" t="n">
-        <v>3280000</v>
+        <v>247976000</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3812,11 +3812,11 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -3829,81 +3829,81 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B40" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>9116</v>
+        <v>11024</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="J40" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>8001</v>
+        <v>6012</v>
       </c>
       <c r="N40" t="n">
-        <v>35386354</v>
+        <v>2000000</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R40" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -3916,10 +3916,358 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5511</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>11026</v>
+      </c>
+      <c r="H41" t="n">
+        <v>17</v>
+      </c>
+      <c r="I41" t="n">
+        <v>512</v>
+      </c>
+      <c r="J41" t="n">
+        <v>21</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8012</v>
+      </c>
+      <c r="N41" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>4613</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5261</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>9927</v>
+      </c>
+      <c r="H42" t="n">
+        <v>26</v>
+      </c>
+      <c r="I42" t="n">
+        <v>783</v>
+      </c>
+      <c r="J42" t="n">
+        <v>705</v>
+      </c>
+      <c r="K42" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11</v>
+      </c>
+      <c r="M42" t="n">
+        <v>8011</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>4511</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>11101</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>10882</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>126</v>
+      </c>
+      <c r="J43" t="n">
+        <v>30</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6006</v>
+      </c>
+      <c r="N43" t="n">
+        <v>13233200</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>4613</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>9116</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>126</v>
+      </c>
+      <c r="J44" t="n">
+        <v>30</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>8001</v>
+      </c>
+      <c r="N44" t="n">
+        <v>38099783</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
           <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>4817</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
         <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -534,7 +534,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
@@ -621,7 +621,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
@@ -664,7 +664,7 @@
         <v>3015</v>
       </c>
       <c r="N3" t="n">
-        <v>6380000</v>
+        <v>3500000</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
@@ -751,7 +751,7 @@
         <v>3015</v>
       </c>
       <c r="N4" t="n">
-        <v>6240000</v>
+        <v>4655000</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
@@ -904,35 +904,35 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11021</v>
+        <v>11280</v>
       </c>
       <c r="H6" t="n">
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J6" t="n">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>6009</v>
+        <v>3012</v>
       </c>
       <c r="N6" t="n">
-        <v>50000000</v>
+        <v>5000000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -949,27 +949,27 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1056,7 +1056,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>11022</v>
+        <v>11021</v>
       </c>
       <c r="H8" t="n">
         <v>17</v>
@@ -1090,23 +1090,23 @@
         <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>8008</v>
+        <v>6009</v>
       </c>
       <c r="N8" t="n">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1115,11 +1115,11 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4611</v>
+        <v>4614</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>TERRENOS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="n">
         <v>1220</v>
@@ -1186,7 +1186,7 @@
         <v>8008</v>
       </c>
       <c r="N9" t="n">
-        <v>350000000</v>
+        <v>95000000</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4613</v>
+        <v>4611</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>TERRENOS</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="n">
         <v>1220</v>
@@ -1273,7 +1273,7 @@
         <v>8008</v>
       </c>
       <c r="N10" t="n">
-        <v>983250000</v>
+        <v>350000000</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>22199</v>
+        <v>21204</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
@@ -1360,7 +1360,7 @@
         <v>8008</v>
       </c>
       <c r="N11" t="n">
-        <v>54750000</v>
+        <v>2510000000</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1384,11 +1384,11 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1404,7 +1404,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
@@ -1447,7 +1447,7 @@
         <v>8008</v>
       </c>
       <c r="N12" t="n">
-        <v>40000000</v>
+        <v>100000000</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1463,19 +1463,19 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1491,7 +1491,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>11023</v>
+        <v>11022</v>
       </c>
       <c r="H13" t="n">
         <v>17</v>
@@ -1528,20 +1528,20 @@
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>8009</v>
+        <v>8008</v>
       </c>
       <c r="N13" t="n">
-        <v>48428689</v>
+        <v>40000000</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1550,24 +1550,24 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>51000</v>
+        <v>22199</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1578,7 +1578,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
@@ -1592,56 +1592,56 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5121</v>
+        <v>5081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10542</v>
+        <v>11023</v>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I14" t="n">
-        <v>752</v>
+        <v>512</v>
       </c>
       <c r="J14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>3010</v>
+        <v>8009</v>
       </c>
       <c r="N14" t="n">
-        <v>259985809</v>
+        <v>55500000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1654,18 +1654,18 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>9994</v>
+        <v>10542</v>
       </c>
       <c r="H15" t="n">
         <v>25</v>
@@ -1702,33 +1702,33 @@
         <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="N15" t="n">
-        <v>4440000</v>
+        <v>70784312</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>4614</v>
+        <v>4511</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1752,7 +1752,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
@@ -1766,43 +1766,43 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>9723</v>
+        <v>9994</v>
       </c>
       <c r="H16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I16" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J16" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="N16" t="n">
-        <v>500000</v>
+        <v>2347000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
@@ -1853,56 +1853,56 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>5191</v>
+        <v>5131</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9796</v>
+        <v>9723</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I17" t="n">
         <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>6011</v>
+        <v>6008</v>
       </c>
       <c r="N17" t="n">
-        <v>243000</v>
+        <v>250000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -1915,18 +1915,18 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>11036</v>
+        <v>9796</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -1957,26 +1957,26 @@
         <v>122</v>
       </c>
       <c r="J18" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M18" t="n">
-        <v>6003</v>
+        <v>6011</v>
       </c>
       <c r="N18" t="n">
-        <v>1000</v>
+        <v>240000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1985,35 +1985,35 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4819</v>
+        <v>4817</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
@@ -2056,7 +2056,7 @@
         <v>6003</v>
       </c>
       <c r="N19" t="n">
-        <v>9256395</v>
+        <v>1000</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2080,11 +2080,11 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2100,7 +2100,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
@@ -2122,72 +2122,72 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9058</v>
+        <v>11036</v>
       </c>
       <c r="H20" t="n">
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>6001</v>
+        <v>6003</v>
       </c>
       <c r="N20" t="n">
-        <v>1000</v>
+        <v>1461000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4511</v>
+        <v>4819</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
@@ -2254,11 +2254,11 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2274,7 +2274,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
@@ -2288,80 +2288,80 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>9087</v>
+        <v>9058</v>
       </c>
       <c r="H22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>6004</v>
+        <v>6001</v>
       </c>
       <c r="N22" t="n">
-        <v>26253389</v>
+        <v>1000</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4813</v>
+        <v>4511</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T22" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
@@ -2383,35 +2383,35 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>11046</v>
+        <v>9087</v>
       </c>
       <c r="H23" t="n">
         <v>23</v>
       </c>
       <c r="I23" t="n">
-        <v>694</v>
+        <v>122</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>8003</v>
+        <v>6004</v>
       </c>
       <c r="N23" t="n">
-        <v>250000000</v>
+        <v>30022403</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2420,11 +2420,11 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4819</v>
+        <v>4813</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2437,18 +2437,18 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>10991</v>
+        <v>11046</v>
       </c>
       <c r="H24" t="n">
         <v>23</v>
@@ -2479,26 +2479,26 @@
         <v>694</v>
       </c>
       <c r="J24" t="n">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>8006</v>
+        <v>8003</v>
       </c>
       <c r="N24" t="n">
-        <v>600000000</v>
+        <v>250000000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2524,18 +2524,18 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
@@ -2549,80 +2549,80 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>11027</v>
+        <v>11249</v>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I25" t="n">
-        <v>121</v>
+        <v>694</v>
       </c>
       <c r="J25" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>3018</v>
+        <v>8004</v>
       </c>
       <c r="N25" t="n">
-        <v>285487805</v>
+        <v>500000000</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4613</v>
+        <v>4819</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T25" t="n">
-        <v>61000</v>
+        <v>12400</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>OUTRAS ORIGENS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
@@ -2636,80 +2636,80 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>5381</v>
+        <v>5201</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9239</v>
+        <v>10991</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="I26" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="J26" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>8002</v>
+        <v>8006</v>
       </c>
       <c r="N26" t="n">
-        <v>5450000</v>
+        <v>600000000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4614</v>
+        <v>4819</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T26" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
@@ -2723,56 +2723,56 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>5381</v>
+        <v>5251</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>9239</v>
+        <v>11027</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J27" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M27" t="n">
-        <v>8002</v>
+        <v>3018</v>
       </c>
       <c r="N27" t="n">
-        <v>400000</v>
+        <v>191687487</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4615</v>
+        <v>4819</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -2785,18 +2785,18 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
@@ -2839,7 +2839,7 @@
         <v>8002</v>
       </c>
       <c r="N28" t="n">
-        <v>4000000</v>
+        <v>9152200</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2851,15 +2851,15 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>4817</v>
+        <v>4614</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
@@ -2926,7 +2926,7 @@
         <v>8002</v>
       </c>
       <c r="N29" t="n">
-        <v>1000</v>
+        <v>522300</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2938,23 +2938,23 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4819</v>
+        <v>4615</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -2970,7 +2970,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
@@ -2984,56 +2984,56 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9420</v>
+        <v>9239</v>
       </c>
       <c r="H30" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J30" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="N30" t="n">
-        <v>231539977</v>
+        <v>12880000</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4613</v>
+        <v>4817</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3046,18 +3046,18 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
@@ -3071,80 +3071,80 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9421</v>
+        <v>9239</v>
       </c>
       <c r="H31" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J31" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3005</v>
+        <v>8002</v>
       </c>
       <c r="N31" t="n">
-        <v>216613767</v>
+        <v>1000</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4613</v>
+        <v>4819</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>9430</v>
+        <v>9420</v>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -3181,20 +3181,20 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="N32" t="n">
-        <v>42479000</v>
+        <v>343756125</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3203,11 +3203,11 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3231,7 +3231,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>11134</v>
+        <v>9421</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -3268,33 +3268,33 @@
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M33" t="n">
-        <v>3009</v>
+        <v>3005</v>
       </c>
       <c r="N33" t="n">
-        <v>92271447</v>
+        <v>285714873</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
+          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B34" t="n">
         <v>1220</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>10062</v>
+        <v>9430</v>
       </c>
       <c r="H34" t="n">
         <v>25</v>
@@ -3349,26 +3349,26 @@
         <v>752</v>
       </c>
       <c r="J34" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="N34" t="n">
-        <v>100000</v>
+        <v>65874000</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3377,11 +3377,11 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3394,18 +3394,18 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B35" t="n">
         <v>1220</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9440</v>
+        <v>11134</v>
       </c>
       <c r="H35" t="n">
         <v>25</v>
@@ -3436,39 +3436,39 @@
         <v>752</v>
       </c>
       <c r="J35" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>3007</v>
+        <v>3009</v>
       </c>
       <c r="N35" t="n">
-        <v>96218712</v>
+        <v>8146743</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>4614</v>
+        <v>4511</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3481,18 +3481,18 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B36" t="n">
         <v>1220</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9450</v>
+        <v>10062</v>
       </c>
       <c r="H36" t="n">
         <v>25</v>
@@ -3529,20 +3529,20 @@
         <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>3008</v>
+        <v>3001</v>
       </c>
       <c r="N36" t="n">
-        <v>18091000</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3551,11 +3551,11 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -3579,7 +3579,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="n">
         <v>1220</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>10677</v>
+        <v>9440</v>
       </c>
       <c r="H37" t="n">
         <v>25</v>
@@ -3616,33 +3616,33 @@
         <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M37" t="n">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="N37" t="n">
-        <v>190392082</v>
+        <v>65661789</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>4511</v>
+        <v>4614</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -3666,7 +3666,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="n">
         <v>1220</v>
@@ -3680,15 +3680,15 @@
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9332</v>
+        <v>9450</v>
       </c>
       <c r="H38" t="n">
         <v>25</v>
@@ -3697,26 +3697,26 @@
         <v>752</v>
       </c>
       <c r="J38" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K38" t="n">
         <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="N38" t="n">
-        <v>4721877188</v>
+        <v>42279000</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3725,11 +3725,11 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -3742,18 +3742,18 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="n">
         <v>1220</v>
@@ -3767,15 +3767,15 @@
         <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>9408</v>
+        <v>10677</v>
       </c>
       <c r="H39" t="n">
         <v>25</v>
@@ -3784,39 +3784,39 @@
         <v>752</v>
       </c>
       <c r="J39" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K39" t="n">
         <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M39" t="n">
-        <v>3003</v>
+        <v>3014</v>
       </c>
       <c r="N39" t="n">
-        <v>247976000</v>
+        <v>116689303</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R39" t="n">
-        <v>4614</v>
+        <v>4511</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -3829,18 +3829,18 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="n">
         <v>1220</v>
@@ -3854,43 +3854,43 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>11024</v>
+        <v>9332</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I40" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J40" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>6012</v>
+        <v>3002</v>
       </c>
       <c r="N40" t="n">
-        <v>2000000</v>
+        <v>5072587386</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3899,11 +3899,11 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -3916,18 +3916,18 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
+          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="n">
         <v>1220</v>
@@ -3941,43 +3941,43 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>5511</v>
+        <v>5401</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>11026</v>
+        <v>9408</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I41" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J41" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="K41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>8012</v>
+        <v>3003</v>
       </c>
       <c r="N41" t="n">
-        <v>45000000</v>
+        <v>233275000</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3986,11 +3986,11 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4003,155 +4003,155 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>5261</v>
+        <v>5511</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>9927</v>
+        <v>11024</v>
       </c>
       <c r="H42" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I42" t="n">
-        <v>783</v>
+        <v>512</v>
       </c>
       <c r="J42" t="n">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="K42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>8011</v>
+        <v>6012</v>
       </c>
       <c r="N42" t="n">
-        <v>1000</v>
+        <v>2500000</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R42" t="n">
-        <v>4511</v>
+        <v>4614</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T42" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10882</v>
+        <v>11026</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="J43" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>6006</v>
+        <v>8012</v>
       </c>
       <c r="N43" t="n">
-        <v>13233200</v>
+        <v>10000000</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -4160,11 +4160,11 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>4613</v>
+        <v>4611</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>TERRENOS</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4177,81 +4177,81 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B44" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>5141</v>
+        <v>5511</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>9116</v>
+        <v>11026</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="J44" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
         <v>8</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M44" t="n">
-        <v>8001</v>
+        <v>8012</v>
       </c>
       <c r="N44" t="n">
-        <v>38099783</v>
+        <v>30000000</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>4817</v>
+        <v>4613</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4264,10 +4264,358 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5511</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>11026</v>
+      </c>
+      <c r="H45" t="n">
+        <v>17</v>
+      </c>
+      <c r="I45" t="n">
+        <v>512</v>
+      </c>
+      <c r="J45" t="n">
+        <v>21</v>
+      </c>
+      <c r="K45" t="n">
+        <v>8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>12</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8012</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>4614</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5261</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>9927</v>
+      </c>
+      <c r="H46" t="n">
+        <v>26</v>
+      </c>
+      <c r="I46" t="n">
+        <v>783</v>
+      </c>
+      <c r="J46" t="n">
+        <v>705</v>
+      </c>
+      <c r="K46" t="n">
+        <v>8</v>
+      </c>
+      <c r="L46" t="n">
+        <v>11</v>
+      </c>
+      <c r="M46" t="n">
+        <v>8011</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>4511</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>11101</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>10882</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>126</v>
+      </c>
+      <c r="J47" t="n">
+        <v>30</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" t="n">
+        <v>6006</v>
+      </c>
+      <c r="N47" t="n">
+        <v>23614000</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>4613</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5141</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>9116</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>126</v>
+      </c>
+      <c r="J48" t="n">
+        <v>30</v>
+      </c>
+      <c r="K48" t="n">
+        <v>8</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>8001</v>
+      </c>
+      <c r="N48" t="n">
+        <v>20445642</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
           <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>4817</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
         <is>
           <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -534,14 +534,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B2" t="n">
         <v>1220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CODEMIG</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -555,9 +555,6 @@
           <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>10929</v>
-      </c>
       <c r="H2" t="n">
         <v>4</v>
       </c>
@@ -577,14 +574,14 @@
         <v>3017</v>
       </c>
       <c r="N2" t="n">
-        <v>1000</v>
+        <v>800000</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+          <t xml:space="preserve"> MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -593,12 +590,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T2" t="n">
         <v>51000</v>
@@ -610,7 +602,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
+          <t xml:space="preserve"> MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -621,35 +613,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B3" t="n">
         <v>1220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CODEMIG</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>5031</v>
+        <v>5011</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>10927</v>
+          <t>COMPANHIA DE DESENVOLVIMENTO ECONÔMICO DE MINAS GERAIS - CODEMIG</t>
+        </is>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>572</v>
+        <v>122</v>
       </c>
       <c r="J3" t="n">
         <v>133</v>
@@ -658,20 +647,20 @@
         <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="N3" t="n">
-        <v>3500000</v>
+        <v>800000</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+          <t xml:space="preserve"> MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -680,12 +669,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T3" t="n">
         <v>51000</v>
@@ -697,7 +681,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
+          <t xml:space="preserve"> MANUTENÇÃO E AQUISIÇÕES DA CODEMIG</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -708,14 +692,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B4" t="n">
         <v>1220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CODEMGE</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -729,9 +713,6 @@
           <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>10927</v>
-      </c>
       <c r="H4" t="n">
         <v>19</v>
       </c>
@@ -751,7 +732,7 @@
         <v>3015</v>
       </c>
       <c r="N4" t="n">
-        <v>4655000</v>
+        <v>4782988</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -767,12 +748,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T4" t="n">
         <v>51000</v>
@@ -795,57 +771,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" t="n">
         <v>1220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CODEMGE</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5071</v>
+        <v>5031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>9775</v>
+          <t>COMPANHIA DE DESENVOLVIMENTO DE MINAS GERAIS - CODEMGE</t>
+        </is>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>122</v>
+        <v>572</v>
       </c>
       <c r="J5" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
-        <v>6010</v>
+        <v>3015</v>
       </c>
       <c r="N5" t="n">
-        <v>120000</v>
+        <v>22047416</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -856,11 +829,6 @@
       <c r="R5" t="n">
         <v>4614</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
       <c r="T5" t="n">
         <v>51000</v>
       </c>
@@ -871,68 +839,65 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
+          <t>GESTÃO DE INFRAESTRUTURA, CONSÓRCIOS E EQUIPAMENTOS CULTURAIS E TURÍSTICOS</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B6" t="n">
         <v>1220</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>11280</v>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>511</v>
+        <v>752</v>
       </c>
       <c r="J6" t="n">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="N6" t="n">
-        <v>5000000</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
+          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -943,11 +908,6 @@
       <c r="R6" t="n">
         <v>4614</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
       <c r="T6" t="n">
         <v>51000</v>
       </c>
@@ -958,68 +918,65 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DOAÇÃO DE MÓDULOS DE FOSSAS SÉPTICAS PARA MUNICÍPIOS SEM CONCESSÃO COPASA (CONVÊNIO DEFESA CIVIL)</t>
+          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PROGRAMA ENCONTRO DAS ÁGUAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B7" t="n">
         <v>1220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>5081</v>
+        <v>5121</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>11021</v>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>512</v>
+        <v>752</v>
       </c>
       <c r="J7" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
-        <v>6009</v>
+        <v>3011</v>
       </c>
       <c r="N7" t="n">
-        <v>50000000</v>
+        <v>5282465</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1030,83 +987,75 @@
       <c r="R7" t="n">
         <v>4614</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
       <c r="T7" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B8" t="n">
         <v>1220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - INVEST MINAS</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>5081</v>
+        <v>5131</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>11021</v>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="J8" t="n">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="N8" t="n">
-        <v>50000000</v>
+        <v>323000</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1115,12 +1064,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4610</v>
       </c>
       <c r="T8" t="n">
         <v>51000</v>
@@ -1132,68 +1076,65 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - COPASA</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B9" t="n">
-        <v>1220</v>
+        <v>1500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - PRODEMGE</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5081</v>
+        <v>5141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>11022</v>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>512</v>
+        <v>126</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>8008</v>
+        <v>6006</v>
       </c>
       <c r="N9" t="n">
-        <v>95000000</v>
+        <v>16317109</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1202,12 +1143,7 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4611</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>TERRENOS</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T9" t="n">
         <v>51000</v>
@@ -1219,256 +1155,232 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B10" t="n">
-        <v>1220</v>
+        <v>1500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - PRODEMGE</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>5081</v>
+        <v>5141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>11022</v>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+        </is>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>512</v>
+        <v>126</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>8008</v>
+        <v>8001</v>
       </c>
       <c r="N10" t="n">
-        <v>350000000</v>
+        <v>58031337</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4817</v>
       </c>
       <c r="T10" t="n">
-        <v>21204</v>
+        <v>51000</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>OP CRÉD CONTRAT EXTERNA - KFW</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B11" t="n">
         <v>1220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>5081</v>
+        <v>5191</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>11022</v>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+        </is>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>512</v>
+        <v>123</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>8008</v>
+        <v>6001</v>
       </c>
       <c r="N11" t="n">
-        <v>2510000000</v>
+        <v>1000</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4511</v>
       </c>
       <c r="T11" t="n">
-        <v>22199</v>
+        <v>11101</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B12" t="n">
         <v>1220</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>5081</v>
+        <v>5191</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>11022</v>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+        </is>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>512</v>
+        <v>123</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>8008</v>
+        <v>6001</v>
       </c>
       <c r="N12" t="n">
-        <v>100000000</v>
+        <v>1000</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4511</v>
       </c>
       <c r="T12" t="n">
         <v>51000</v>
@@ -1480,256 +1392,232 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B13" t="n">
         <v>1220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>5081</v>
+        <v>5191</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>11022</v>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+        </is>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="J13" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M13" t="n">
-        <v>8008</v>
+        <v>6011</v>
       </c>
       <c r="N13" t="n">
-        <v>40000000</v>
+        <v>555000</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4817</v>
       </c>
       <c r="T13" t="n">
-        <v>22199</v>
+        <v>51000</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>OP CRÉD A CONTRATAR INTERNA - OUTRAS</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DA COPASA</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B14" t="n">
         <v>1220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>5081</v>
+        <v>5191</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>COMPANHIA DE SANEAMENTO DE MINAS GERAIS - COPASA</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>11023</v>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+        </is>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="J14" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>8009</v>
+        <v>6003</v>
       </c>
       <c r="N14" t="n">
-        <v>55500000</v>
+        <v>1000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4819</v>
       </c>
       <c r="T14" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>PPP SISTEMA ADUTOR RIO MANSO</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
+          <t>Apoio ao Desenvolvimento Municipal e à Coordenação das Transferências Estaduais de Recursos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B15" t="n">
         <v>1220</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>5121</v>
+        <v>5191</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>10542</v>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+        </is>
       </c>
       <c r="H15" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J15" t="n">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3010</v>
+        <v>6003</v>
       </c>
       <c r="N15" t="n">
-        <v>70784312</v>
+        <v>664500</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+        <v>4819</v>
       </c>
       <c r="T15" t="n">
         <v>51000</v>
@@ -1741,242 +1629,223 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>Apoio ao Desenvolvimento Municipal e à Coordenação das Transferências Estaduais de Recursos Financeiros</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B16" t="n">
         <v>1220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - BDMG</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5121</v>
+        <v>5201</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>9994</v>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+        </is>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I16" t="n">
-        <v>752</v>
+        <v>694</v>
       </c>
       <c r="J16" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3011</v>
+        <v>8003</v>
       </c>
       <c r="N16" t="n">
-        <v>2347000</v>
+        <v>260000000</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4810</v>
       </c>
       <c r="T16" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B17" t="n">
         <v>1220</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - BDMG</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>5131</v>
+        <v>5201</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>9723</v>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+        </is>
       </c>
       <c r="H17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
         <v>122</v>
       </c>
       <c r="J17" t="n">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>6008</v>
+        <v>6004</v>
       </c>
       <c r="N17" t="n">
-        <v>250000</v>
+        <v>38941920</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4813</v>
       </c>
       <c r="T17" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL  DO BDMG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B18" t="n">
         <v>1220</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - BDMG</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>5191</v>
+        <v>5201</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>9796</v>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+        </is>
       </c>
       <c r="H18" t="n">
+        <v>23</v>
+      </c>
+      <c r="I18" t="n">
+        <v>694</v>
+      </c>
+      <c r="J18" t="n">
+        <v>107</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
-        <v>122</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>11</v>
-      </c>
       <c r="M18" t="n">
-        <v>6011</v>
+        <v>8004</v>
       </c>
       <c r="N18" t="n">
-        <v>240000</v>
+        <v>825000000</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1985,144 +1854,128 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4817</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+        <v>4810</v>
       </c>
       <c r="T18" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t xml:space="preserve">FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B19" t="n">
         <v>1220</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - GASMIG</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5191</v>
+        <v>5251</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>11036</v>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+        </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J19" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>6003</v>
+        <v>3018</v>
       </c>
       <c r="N19" t="n">
-        <v>1000</v>
+        <v>457766318</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T19" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B20" t="n">
         <v>1220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5191</v>
+        <v>5381</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>11036</v>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+        </is>
       </c>
       <c r="H20" t="n">
         <v>4</v>
@@ -2131,40 +1984,35 @@
         <v>122</v>
       </c>
       <c r="J20" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>6003</v>
+        <v>8002</v>
       </c>
       <c r="N20" t="n">
-        <v>1461000</v>
+        <v>12650330</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T20" t="n">
         <v>51000</v>
@@ -2176,145 +2024,134 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>APOIO AO DESENVOLVIMENTO MUNICIPAL E À COORDENAÇÃO DAS TRANSFERÊNCIAS ESTADUAIS DE RECURSOS FINANCEIROS</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B21" t="n">
         <v>1220</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>5191</v>
+        <v>5381</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>9058</v>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+        </is>
       </c>
       <c r="H21" t="n">
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>6001</v>
+        <v>8002</v>
       </c>
       <c r="N21" t="n">
-        <v>1000</v>
+        <v>524600</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+        <v>4615</v>
       </c>
       <c r="T21" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B22" t="n">
         <v>1220</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5191</v>
+        <v>5381</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>9058</v>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+        </is>
       </c>
       <c r="H22" t="n">
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>6001</v>
+        <v>8002</v>
       </c>
       <c r="N22" t="n">
         <v>1000</v>
@@ -2324,94 +2161,86 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
+        <v>4810</v>
       </c>
       <c r="T22" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B23" t="n">
         <v>1220</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5201</v>
+        <v>5381</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>9087</v>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
         <v>122</v>
       </c>
       <c r="J23" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>6004</v>
+        <v>8002</v>
       </c>
       <c r="N23" t="n">
-        <v>30022403</v>
+        <v>4842500</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2420,360 +2249,323 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4813</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
-        </is>
+        <v>4817</v>
       </c>
       <c r="T23" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B24" t="n">
         <v>1220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>5201</v>
+        <v>5391</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>11046</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I24" t="n">
-        <v>694</v>
+        <v>752</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>8003</v>
+        <v>3004</v>
       </c>
       <c r="N24" t="n">
-        <v>250000000</v>
+        <v>228410975</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T24" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B25" t="n">
         <v>1220</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5201</v>
+        <v>5391</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>11249</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>694</v>
+        <v>752</v>
       </c>
       <c r="J25" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>8004</v>
+        <v>3005</v>
       </c>
       <c r="N25" t="n">
-        <v>500000000</v>
+        <v>426883823</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T25" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B26" t="n">
         <v>1220</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>5201</v>
+        <v>5391</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>10991</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I26" t="n">
-        <v>694</v>
+        <v>752</v>
       </c>
       <c r="J26" t="n">
-        <v>171</v>
+        <v>92</v>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
         <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>8006</v>
+        <v>3006</v>
       </c>
       <c r="N26" t="n">
-        <v>600000000</v>
+        <v>32235731</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T26" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À INFRAESTRUTURA E AO DESENVOLVIMENTO SUSTENTÁVEL EM MG ENTRE BDMG E NEW DEVELOPMENT BANK (BDMG INFRA ODS)</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B27" t="n">
         <v>1220</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>5251</v>
+        <v>5391</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>11027</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>121</v>
+        <v>752</v>
       </c>
       <c r="J27" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M27" t="n">
-        <v>3018</v>
+        <v>3009</v>
       </c>
       <c r="N27" t="n">
-        <v>191687487</v>
+        <v>56493213</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T27" t="n">
         <v>51000</v>
@@ -2785,68 +2577,65 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B28" t="n">
         <v>1220</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>9239</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I28" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J28" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>8002</v>
+        <v>3001</v>
       </c>
       <c r="N28" t="n">
-        <v>9152200</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2855,12 +2644,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
+        <v>4613</v>
       </c>
       <c r="T28" t="n">
         <v>51000</v>
@@ -2872,68 +2656,65 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B29" t="n">
         <v>1220</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>9239</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I29" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J29" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="K29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>8002</v>
+        <v>3007</v>
       </c>
       <c r="N29" t="n">
-        <v>522300</v>
+        <v>121588957</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2942,12 +2723,7 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4615</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T29" t="n">
         <v>51000</v>
@@ -2959,82 +2735,74 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B30" t="n">
         <v>1220</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>9239</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I30" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J30" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
         <v>8</v>
       </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
       <c r="M30" t="n">
-        <v>8002</v>
+        <v>3008</v>
       </c>
       <c r="N30" t="n">
-        <v>12880000</v>
+        <v>28627843</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4817</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T30" t="n">
         <v>51000</v>
@@ -3046,127 +2814,116 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B31" t="n">
         <v>1220</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5381</v>
+        <v>5391</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>9239</v>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+        </is>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I31" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J31" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M31" t="n">
-        <v>8002</v>
+        <v>3014</v>
       </c>
       <c r="N31" t="n">
-        <v>1000</v>
+        <v>1080197578</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4819</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>OUTRAS APLICAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T31" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B32" t="n">
         <v>1220</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>5391</v>
+        <v>5401</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>9420</v>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+        </is>
       </c>
       <c r="H32" t="n">
         <v>25</v>
@@ -3175,26 +2932,26 @@
         <v>752</v>
       </c>
       <c r="J32" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="N32" t="n">
-        <v>343756125</v>
+        <v>5320034427</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3203,12 +2960,7 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T32" t="n">
         <v>51000</v>
@@ -3220,40 +2972,37 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B33" t="n">
         <v>1220</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>5391</v>
+        <v>5401</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>9421</v>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+        </is>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -3262,26 +3011,26 @@
         <v>752</v>
       </c>
       <c r="J33" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="N33" t="n">
-        <v>285714873</v>
+        <v>250370467</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3290,12 +3039,7 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
+        <v>4614</v>
       </c>
       <c r="T33" t="n">
         <v>51000</v>
@@ -3307,1317 +3051,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO</t>
+          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>9430</v>
-      </c>
-      <c r="H34" t="n">
-        <v>25</v>
-      </c>
-      <c r="I34" t="n">
-        <v>752</v>
-      </c>
-      <c r="J34" t="n">
-        <v>92</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3006</v>
-      </c>
-      <c r="N34" t="n">
-        <v>65874000</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T34" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>11134</v>
-      </c>
-      <c r="H35" t="n">
-        <v>25</v>
-      </c>
-      <c r="I35" t="n">
-        <v>752</v>
-      </c>
-      <c r="J35" t="n">
-        <v>92</v>
-      </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" t="n">
-        <v>9</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3009</v>
-      </c>
-      <c r="N35" t="n">
-        <v>8146743</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
-      </c>
-      <c r="T35" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>10062</v>
-      </c>
-      <c r="H36" t="n">
-        <v>25</v>
-      </c>
-      <c r="I36" t="n">
-        <v>752</v>
-      </c>
-      <c r="J36" t="n">
-        <v>94</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3001</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
-      </c>
-      <c r="T36" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>9440</v>
-      </c>
-      <c r="H37" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" t="n">
-        <v>752</v>
-      </c>
-      <c r="J37" t="n">
-        <v>94</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3007</v>
-      </c>
-      <c r="N37" t="n">
-        <v>65661789</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T37" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>9450</v>
-      </c>
-      <c r="H38" t="n">
-        <v>25</v>
-      </c>
-      <c r="I38" t="n">
-        <v>752</v>
-      </c>
-      <c r="J38" t="n">
-        <v>94</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>8</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3008</v>
-      </c>
-      <c r="N38" t="n">
-        <v>42279000</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T38" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" t="n">
-        <v>5391</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>10677</v>
-      </c>
-      <c r="H39" t="n">
-        <v>25</v>
-      </c>
-      <c r="I39" t="n">
-        <v>752</v>
-      </c>
-      <c r="J39" t="n">
-        <v>94</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>14</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3014</v>
-      </c>
-      <c r="N39" t="n">
-        <v>116689303</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
-      </c>
-      <c r="T39" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>GERAÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B40" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5401</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>9332</v>
-      </c>
-      <c r="H40" t="n">
-        <v>25</v>
-      </c>
-      <c r="I40" t="n">
-        <v>752</v>
-      </c>
-      <c r="J40" t="n">
-        <v>72</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3002</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5072587386</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R40" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
-      </c>
-      <c r="T40" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD)</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
           <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B41" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5401</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>9408</v>
-      </c>
-      <c r="H41" t="n">
-        <v>25</v>
-      </c>
-      <c r="I41" t="n">
-        <v>752</v>
-      </c>
-      <c r="J41" t="n">
-        <v>72</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3</v>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3003</v>
-      </c>
-      <c r="N41" t="n">
-        <v>233275000</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R41" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T41" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B42" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" t="n">
-        <v>5511</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>11024</v>
-      </c>
-      <c r="H42" t="n">
-        <v>17</v>
-      </c>
-      <c r="I42" t="n">
-        <v>512</v>
-      </c>
-      <c r="J42" t="n">
-        <v>21</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" t="n">
-        <v>12</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6012</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R42" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T42" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B43" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" t="n">
-        <v>5511</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>11026</v>
-      </c>
-      <c r="H43" t="n">
-        <v>17</v>
-      </c>
-      <c r="I43" t="n">
-        <v>512</v>
-      </c>
-      <c r="J43" t="n">
-        <v>21</v>
-      </c>
-      <c r="K43" t="n">
-        <v>8</v>
-      </c>
-      <c r="L43" t="n">
-        <v>12</v>
-      </c>
-      <c r="M43" t="n">
-        <v>8012</v>
-      </c>
-      <c r="N43" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R43" t="n">
-        <v>4611</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>TERRENOS</t>
-        </is>
-      </c>
-      <c r="T43" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B44" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" t="n">
-        <v>5511</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>11026</v>
-      </c>
-      <c r="H44" t="n">
-        <v>17</v>
-      </c>
-      <c r="I44" t="n">
-        <v>512</v>
-      </c>
-      <c r="J44" t="n">
-        <v>21</v>
-      </c>
-      <c r="K44" t="n">
-        <v>8</v>
-      </c>
-      <c r="L44" t="n">
-        <v>12</v>
-      </c>
-      <c r="M44" t="n">
-        <v>8012</v>
-      </c>
-      <c r="N44" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R44" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
-      </c>
-      <c r="T44" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B45" t="n">
-        <v>1220</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - SEDE</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="n">
-        <v>5511</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>COPASA - SERVIÇOS DE SANEAMENTO INTEGRADO DO NORTE E NORDESTE DE MINAS GERAIS S/A - COPANOR</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>11026</v>
-      </c>
-      <c r="H45" t="n">
-        <v>17</v>
-      </c>
-      <c r="I45" t="n">
-        <v>512</v>
-      </c>
-      <c r="J45" t="n">
-        <v>21</v>
-      </c>
-      <c r="K45" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" t="n">
-        <v>12</v>
-      </c>
-      <c r="M45" t="n">
-        <v>8012</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>4614</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
-        </is>
-      </c>
-      <c r="T45" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>UNIVERSALIZAÇÃO DOS SERVIÇOS DE SANEAMENTO NA ÁREA DE ATUAÇÃO DA COPANOR</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SANEAMENTO E RESÍDUOS ESPECIAIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B46" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - SEINFRA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5261</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>9927</v>
-      </c>
-      <c r="H46" t="n">
-        <v>26</v>
-      </c>
-      <c r="I46" t="n">
-        <v>783</v>
-      </c>
-      <c r="J46" t="n">
-        <v>705</v>
-      </c>
-      <c r="K46" t="n">
-        <v>8</v>
-      </c>
-      <c r="L46" t="n">
-        <v>11</v>
-      </c>
-      <c r="M46" t="n">
-        <v>8011</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
-        <v>4511</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SOCIEDADES CONTROLADAS</t>
-        </is>
-      </c>
-      <c r="T46" t="n">
-        <v>11101</v>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B47" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>5141</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>10882</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4</v>
-      </c>
-      <c r="I47" t="n">
-        <v>126</v>
-      </c>
-      <c r="J47" t="n">
-        <v>30</v>
-      </c>
-      <c r="K47" t="n">
-        <v>6</v>
-      </c>
-      <c r="L47" t="n">
-        <v>6</v>
-      </c>
-      <c r="M47" t="n">
-        <v>6006</v>
-      </c>
-      <c r="N47" t="n">
-        <v>23614000</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
-        <v>4613</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>OBRAS E INSTALAÇÕES</t>
-        </is>
-      </c>
-      <c r="T47" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B48" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - SEPLAG</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" t="n">
-        <v>5141</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>9116</v>
-      </c>
-      <c r="H48" t="n">
-        <v>4</v>
-      </c>
-      <c r="I48" t="n">
-        <v>126</v>
-      </c>
-      <c r="J48" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" t="n">
-        <v>8</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>8001</v>
-      </c>
-      <c r="N48" t="n">
-        <v>20445642</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>4817</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
-        </is>
-      </c>
-      <c r="T48" t="n">
-        <v>51000</v>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>RECURSOS PRÓPRIOS</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -592,6 +592,11 @@
       <c r="R2" t="n">
         <v>4613</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>51000</v>
       </c>
@@ -671,6 +676,11 @@
       <c r="R3" t="n">
         <v>4614</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>51000</v>
       </c>
@@ -750,6 +760,11 @@
       <c r="R4" t="n">
         <v>4613</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
       <c r="T4" t="n">
         <v>51000</v>
       </c>
@@ -829,6 +844,11 @@
       <c r="R5" t="n">
         <v>4614</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>51000</v>
       </c>
@@ -908,6 +928,11 @@
       <c r="R6" t="n">
         <v>4614</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T6" t="n">
         <v>51000</v>
       </c>
@@ -987,6 +1012,11 @@
       <c r="R7" t="n">
         <v>4614</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>51000</v>
       </c>
@@ -1066,6 +1096,11 @@
       <c r="R8" t="n">
         <v>4610</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>IMOBILIZAÇÕES</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>51000</v>
       </c>
@@ -1145,6 +1180,11 @@
       <c r="R9" t="n">
         <v>4613</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>51000</v>
       </c>
@@ -1224,6 +1264,11 @@
       <c r="R10" t="n">
         <v>4817</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>51000</v>
       </c>
@@ -1303,6 +1348,11 @@
       <c r="R11" t="n">
         <v>4511</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>11101</v>
       </c>
@@ -1382,6 +1432,11 @@
       <c r="R12" t="n">
         <v>4511</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>51000</v>
       </c>
@@ -1461,6 +1516,11 @@
       <c r="R13" t="n">
         <v>4817</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>51000</v>
       </c>
@@ -1540,6 +1600,11 @@
       <c r="R14" t="n">
         <v>4819</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
       <c r="T14" t="n">
         <v>11101</v>
       </c>
@@ -1619,6 +1684,11 @@
       <c r="R15" t="n">
         <v>4819</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>51000</v>
       </c>
@@ -1698,6 +1768,11 @@
       <c r="R16" t="n">
         <v>4810</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>12400</v>
       </c>
@@ -1777,6 +1852,11 @@
       <c r="R17" t="n">
         <v>4813</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>12400</v>
       </c>
@@ -1856,6 +1936,11 @@
       <c r="R18" t="n">
         <v>4810</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>OUTRAS APLICAÇÕES</t>
+        </is>
+      </c>
       <c r="T18" t="n">
         <v>12400</v>
       </c>
@@ -1935,6 +2020,11 @@
       <c r="R19" t="n">
         <v>4613</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
       <c r="T19" t="n">
         <v>51000</v>
       </c>
@@ -1959,77 +2049,82 @@
         <v>2027</v>
       </c>
       <c r="B20" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5381</v>
+        <v>5261</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I20" t="n">
-        <v>122</v>
+        <v>783</v>
       </c>
       <c r="J20" t="n">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M20" t="n">
-        <v>8002</v>
+        <v>8011</v>
       </c>
       <c r="N20" t="n">
-        <v>12650330</v>
+        <v>1000</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4614</v>
+        <v>4511</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SOCIEDADES CONTROLADAS</t>
+        </is>
       </c>
       <c r="T20" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2170,7 @@
         <v>8002</v>
       </c>
       <c r="N21" t="n">
-        <v>524600</v>
+        <v>12650330</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2091,7 +2186,12 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4615</v>
+        <v>4614</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
       </c>
       <c r="T21" t="n">
         <v>51000</v>
@@ -2154,7 +2254,7 @@
         <v>8002</v>
       </c>
       <c r="N22" t="n">
-        <v>1000</v>
+        <v>524600</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2166,18 +2266,23 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4810</v>
+        <v>4615</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>MÓVEIS E UTENSÍLIOS</t>
+        </is>
       </c>
       <c r="T22" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2233,7 +2338,7 @@
         <v>8002</v>
       </c>
       <c r="N23" t="n">
-        <v>4842500</v>
+        <v>1000</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2249,14 +2354,19 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4817</v>
+        <v>4810</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>OUTRAS APLICAÇÕES</t>
+        </is>
       </c>
       <c r="T23" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2279,56 +2389,61 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J24" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="N24" t="n">
-        <v>228410975</v>
+        <v>4842500</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4613</v>
+        <v>4817</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
+        </is>
       </c>
       <c r="T24" t="n">
         <v>51000</v>
@@ -2340,12 +2455,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
@@ -2385,20 +2500,20 @@
         <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="N25" t="n">
-        <v>426883823</v>
+        <v>228410975</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2409,6 +2524,11 @@
       <c r="R25" t="n">
         <v>4613</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
+      </c>
       <c r="T25" t="n">
         <v>51000</v>
       </c>
@@ -2419,7 +2539,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2464,20 +2584,20 @@
         <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="N26" t="n">
-        <v>32235731</v>
+        <v>426883823</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2486,7 +2606,12 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>4614</v>
+        <v>4613</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
       </c>
       <c r="T26" t="n">
         <v>51000</v>
@@ -2498,7 +2623,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2543,20 +2668,20 @@
         <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>3009</v>
+        <v>3006</v>
       </c>
       <c r="N27" t="n">
-        <v>56493213</v>
+        <v>32235731</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2567,6 +2692,11 @@
       <c r="R27" t="n">
         <v>4614</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>51000</v>
       </c>
@@ -2577,7 +2707,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2616,26 +2746,26 @@
         <v>752</v>
       </c>
       <c r="J28" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>3001</v>
+        <v>3009</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>56493213</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2644,7 +2774,12 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>4613</v>
+        <v>4614</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
       </c>
       <c r="T28" t="n">
         <v>51000</v>
@@ -2656,12 +2791,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
@@ -2701,20 +2836,20 @@
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>3007</v>
+        <v>3001</v>
       </c>
       <c r="N29" t="n">
-        <v>121588957</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2723,7 +2858,12 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4614</v>
+        <v>4613</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALAÇÕES</t>
+        </is>
       </c>
       <c r="T29" t="n">
         <v>51000</v>
@@ -2735,7 +2875,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2780,20 +2920,20 @@
         <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M30" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="N30" t="n">
-        <v>28627843</v>
+        <v>121588957</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2804,6 +2944,11 @@
       <c r="R30" t="n">
         <v>4614</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T30" t="n">
         <v>51000</v>
       </c>
@@ -2814,7 +2959,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -2859,20 +3004,20 @@
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>3014</v>
+        <v>3008</v>
       </c>
       <c r="N31" t="n">
-        <v>1080197578</v>
+        <v>28627843</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2883,6 +3028,11 @@
       <c r="R31" t="n">
         <v>4614</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T31" t="n">
         <v>51000</v>
       </c>
@@ -2893,7 +3043,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -2911,18 +3061,18 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2932,26 +3082,26 @@
         <v>752</v>
       </c>
       <c r="J32" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M32" t="n">
-        <v>3002</v>
+        <v>3014</v>
       </c>
       <c r="N32" t="n">
-        <v>5320034427</v>
+        <v>1080197578</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2962,6 +3112,11 @@
       <c r="R32" t="n">
         <v>4614</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T32" t="n">
         <v>51000</v>
       </c>
@@ -2972,12 +3127,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
@@ -3017,20 +3172,20 @@
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="N33" t="n">
-        <v>250370467</v>
+        <v>5320034427</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3041,6 +3196,11 @@
       <c r="R33" t="n">
         <v>4614</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>51000</v>
       </c>
@@ -3051,10 +3211,94 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5401</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" t="n">
+        <v>752</v>
+      </c>
+      <c r="J34" t="n">
+        <v>72</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3003</v>
+      </c>
+      <c r="N34" t="n">
+        <v>250370467</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
           <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>4614</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -910,7 +910,7 @@
         <v>3010</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -2842,7 +2842,7 @@
         <v>3001</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>

--- a/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
+++ b/bancos/SISOR/BASE_QDD_INVESTIMENTO.xlsx
@@ -877,47 +877,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG HOLDING</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - COHAB</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>5121</v>
+        <v>5071</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
+          <t>COMPANHIA DE HABITAÇÃO DO ESTADO DE MINAS GERAIS - COHAB</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J6" t="n">
-        <v>35</v>
+        <v>705</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>3010</v>
+        <v>6010</v>
       </c>
       <c r="N6" t="n">
-        <v>1000</v>
+        <v>36608798</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA ADMINISTRATIVA - COHAB</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS CEMIG</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
@@ -988,20 +988,20 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="N7" t="n">
-        <v>5282465</v>
+        <v>1000</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
+          <t xml:space="preserve"> INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1045,47 +1045,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - INVEST MINAS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>5131</v>
+        <v>5121</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
+          <t>COMPANHIA ENERGÉTICA DE MINAS GERAIS - CEMIG HOLDING</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>122</v>
+        <v>752</v>
       </c>
       <c r="J8" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>6008</v>
+        <v>3011</v>
       </c>
       <c r="N8" t="n">
-        <v>323000</v>
+        <v>5282465</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1094,11 +1094,11 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>4610</v>
+        <v>4614</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>IMOBILIZAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
+          <t xml:space="preserve"> MANUTENÇÃO DA INFRAESTRUTURA DA CEMIG HOLDING</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
+          <t>INVESTIMENTOS CEMIG</t>
         </is>
       </c>
     </row>
@@ -1125,51 +1125,51 @@
         <v>2027</v>
       </c>
       <c r="B9" t="n">
-        <v>1500</v>
+        <v>1220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - PRODEMGE</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - INVEST MINAS</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>5141</v>
+        <v>5131</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
+          <t>AGÊNCIA DE PROMOÇÃO DE INVESTIMENTOS DE MINAS GERAIS - INVEST MINAS</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>6006</v>
+        <v>6008</v>
       </c>
       <c r="N9" t="n">
-        <v>16317109</v>
+        <v>323000</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>4613</v>
+        <v>4610</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL DA INVEST MINAS</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL - INVEST MINAS</t>
         </is>
       </c>
     </row>
@@ -1237,36 +1237,36 @@
         <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>8001</v>
+        <v>6006</v>
       </c>
       <c r="N10" t="n">
-        <v>58031337</v>
+        <v>16317109</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>4817</v>
+        <v>4613</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>MANUTENÇÃO DAS UNIDADES PREDIAIS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1293,82 +1293,82 @@
         <v>2027</v>
       </c>
       <c r="B11" t="n">
-        <v>1220</v>
+        <v>1500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTÃO - PRODEMGE</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>5191</v>
+        <v>5141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
+          <t>COMPANHIA DE TECNOLOGIA DA INFORMAÇÃO DO ESTADO DE MINAS GERAIS - PRODEMGE</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>6001</v>
+        <v>8001</v>
       </c>
       <c r="N11" t="n">
-        <v>1000</v>
+        <v>58031337</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>4511</v>
+        <v>4817</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>AQUISIÇÃO DE HARDWARES E SOFTWARES PARA PRESTAÇÃO DE SERVIÇOS EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>SOLUÇÕES EM TECNOLOGIA DA INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
@@ -1438,11 +1438,11 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1483,7 +1483,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J13" t="n">
         <v>13</v>
@@ -1492,33 +1492,33 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>6011</v>
+        <v>6001</v>
       </c>
       <c r="N13" t="n">
-        <v>555000</v>
+        <v>1000</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>4817</v>
+        <v>4511</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
+          <t>INVESTIMENTOS VIA PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1570,26 +1570,26 @@
         <v>122</v>
       </c>
       <c r="J14" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>6003</v>
+        <v>6011</v>
       </c>
       <c r="N14" t="n">
-        <v>1000</v>
+        <v>555000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1598,29 +1598,29 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>4819</v>
+        <v>4817</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Apoio ao Desenvolvimento Municipal e à Coordenação das Transferências Estaduais de Recursos Financeiros</t>
+          <t>APORTE DE CAPITAL E MANUTENÇÃO DA INFRAESTRUTURA DA MGI</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
         <v>6003</v>
       </c>
       <c r="N15" t="n">
-        <v>664500</v>
+        <v>1000</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1717,47 +1717,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - BDMG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGI</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5201</v>
+        <v>5191</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
+          <t>MINAS GERAIS PARTICIPAÇÕES S.A - MGI</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>694</v>
+        <v>122</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>8003</v>
+        <v>6003</v>
       </c>
       <c r="N16" t="n">
-        <v>260000000</v>
+        <v>664500</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>4810</v>
+        <v>4819</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>12400</v>
+        <v>51000</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>OUTRAS ENTIDADES - BDMG</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>SUPORTE AO DESENVOLVIMENTO ESTADUAL</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
+          <t>Apoio ao Desenvolvimento Municipal e à Coordenação das Transferências Estaduais de Recursos Financeiros</t>
         </is>
       </c>
     </row>
@@ -1819,29 +1819,29 @@
         <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>122</v>
+        <v>694</v>
       </c>
       <c r="J17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>6004</v>
+        <v>8003</v>
       </c>
       <c r="N17" t="n">
-        <v>38941920</v>
+        <v>260000000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>4813</v>
+        <v>4810</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL  DO BDMG</t>
+          <t>FINANCIAMENTO À DESCARBONIZAÇÃO E RESILIÊNCIA CLIMÁTICA ENTRE BDMG E BANCO INTERAMERICANO DE DESENVOLVIMENTO (BDMG PBR)</t>
         </is>
       </c>
     </row>
@@ -1903,29 +1903,29 @@
         <v>23</v>
       </c>
       <c r="I18" t="n">
-        <v>694</v>
+        <v>122</v>
       </c>
       <c r="J18" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
         <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>8004</v>
+        <v>6004</v>
       </c>
       <c r="N18" t="n">
-        <v>825000000</v>
+        <v>38941920</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>4810</v>
+        <v>4813</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>INTANGÍVEIS E OUTROS INVESTIMENTOS</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL DO BDMG</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE </t>
+          <t>INVESTIMENTO NA INFRAESTRUTURA ADMINISTRATIVA E OPERACIONAL  DO BDMG</t>
         </is>
       </c>
     </row>
@@ -1969,78 +1969,78 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - GASMIG</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - BDMG</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5251</v>
+        <v>5201</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
+          <t>BANCO DE DESENVOLVIMENTO DE MINAS GERAIS S.A - BDMG</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>121</v>
+        <v>694</v>
       </c>
       <c r="J19" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>3018</v>
+        <v>8004</v>
       </c>
       <c r="N19" t="n">
-        <v>457766318</v>
+        <v>825000000</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>4613</v>
+        <v>4810</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>51000</v>
+        <v>12400</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>OUTRAS ENTIDADES - BDMG</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
+          <t>FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE INVESTIMENTO (BDMG SUSTENTABILIDADE E MPE)</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>MINAS GERAÇÃO DE VALOR</t>
+          <t xml:space="preserve">FINANCIAMENTO À SUSTENTABILIDADE E ÀS MICRO E PEQUENAS EMPRESAS DO ESTADO DE MINAS GERAIS ENTRE BDMG E BANCO EUROPEU DE </t>
         </is>
       </c>
     </row>
@@ -2049,82 +2049,82 @@
         <v>2027</v>
       </c>
       <c r="B20" t="n">
-        <v>1300</v>
+        <v>1220</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - TREM METROPOLITANO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - GASMIG</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>5261</v>
+        <v>5251</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
+          <t>COMPANHIA DE GÁS DE MINAS GERAIS - GASMIG</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I20" t="n">
-        <v>783</v>
+        <v>121</v>
       </c>
       <c r="J20" t="n">
-        <v>705</v>
+        <v>133</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M20" t="n">
-        <v>8011</v>
+        <v>3018</v>
       </c>
       <c r="N20" t="n">
-        <v>1000</v>
+        <v>457766318</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>4511</v>
+        <v>4613</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>SOCIEDADES CONTROLADAS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
+          <t>GÁS COMPETITIVO- EXPANSÃO DA REDE DE GÁS NATURAL</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
+          <t>MINAS GERAÇÃO DE VALOR</t>
         </is>
       </c>
     </row>
@@ -2133,82 +2133,82 @@
         <v>2027</v>
       </c>
       <c r="B21" t="n">
-        <v>1220</v>
+        <v>1300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIA - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>5381</v>
+        <v>5261</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
+          <t>TREM METROPOLITANO DE BELO HORIZONTE S.A - TREM METROPOLITANO</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I21" t="n">
-        <v>122</v>
+        <v>783</v>
       </c>
       <c r="J21" t="n">
-        <v>57</v>
+        <v>705</v>
       </c>
       <c r="K21" t="n">
         <v>8</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>8002</v>
+        <v>8011</v>
       </c>
       <c r="N21" t="n">
-        <v>12650330</v>
+        <v>1000</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4510 - PARTICIPAÇÃO SOCIETÁRIA</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>4614</v>
+        <v>4511</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>SOCIEDADES CONTROLADAS</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
+          <t>MANUTENÇÃO E ADEQUAÇÃO DA INFRA-ESTRUTURA ADMINISTRATIVA E OPERACIONAL - TRANSPORTES METROPOLITANOS</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
+          <t>APOIO ÀS POLÍTICAS PÚBLICAS</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
         <v>8002</v>
       </c>
       <c r="N22" t="n">
-        <v>524600</v>
+        <v>12650330</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2270,11 +2270,11 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>4615</v>
+        <v>4614</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>MÓVEIS E UTENSÍLIOS</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2338,7 +2338,7 @@
         <v>8002</v>
       </c>
       <c r="N23" t="n">
-        <v>1000</v>
+        <v>524600</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2350,23 +2350,23 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4810 - OUTRAS APLICAÇÕES</t>
+          <t>4610 - IMOBILIZAÇÕES</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>4810</v>
+        <v>4615</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OUTRAS APLICAÇÕES</t>
+          <t>MÓVEIS E UTENSÍLIOS</t>
         </is>
       </c>
       <c r="T23" t="n">
-        <v>11101</v>
+        <v>51000</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
+          <t>RECURSOS PRÓPRIOS</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2422,7 +2422,7 @@
         <v>8002</v>
       </c>
       <c r="N24" t="n">
-        <v>4842500</v>
+        <v>1000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2438,19 +2438,19 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>4817</v>
+        <v>4810</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>EQUIPAMENTOS E SOFTWARE</t>
+          <t>OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="T24" t="n">
-        <v>51000</v>
+        <v>11101</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS</t>
+          <t>TESOURO ORDINÁRIO - APLICAÇÃO LIVRE</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2473,60 +2473,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - MGS</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5391</v>
+        <v>5381</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
+          <t>MINAS GERAIS ADMINISTRAÇÃO E SERVIÇOS S.A - MGS</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>752</v>
+        <v>122</v>
       </c>
       <c r="J25" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>3004</v>
+        <v>8002</v>
       </c>
       <c r="N25" t="n">
-        <v>228410975</v>
+        <v>4842500</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4610 - IMOBILIZAÇÕES</t>
+          <t>4810 - OUTRAS APLICAÇÕES</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>4613</v>
+        <v>4817</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>EQUIPAMENTOS E SOFTWARE</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
+          <t>INVESTIMENTOS EM ATIVO FIXO PARA PRESTAÇÃO DE SERVIÇO</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
+          <t>SOLUÇÕES EM SERVIÇOS DE APOIO TÉCNICO-OPERACIONAL</t>
         </is>
       </c>
     </row>
@@ -2584,20 +2584,20 @@
         <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="N26" t="n">
-        <v>426883823</v>
+        <v>228410975</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
+          <t>EXPANSÃO DO SISTEMA DE TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2668,20 +2668,20 @@
         <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="N27" t="n">
-        <v>32235731</v>
+        <v>426883823</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2690,11 +2690,11 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
+          <t xml:space="preserve">REFORMAS DE SUBESTAÇÕES E LINHAS DE TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2752,20 +2752,20 @@
         <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>3009</v>
+        <v>3006</v>
       </c>
       <c r="N28" t="n">
-        <v>56493213</v>
+        <v>32235731</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA TRANSMISSÃO</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2830,26 +2830,26 @@
         <v>752</v>
       </c>
       <c r="J29" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>3001</v>
+        <v>3009</v>
       </c>
       <c r="N29" t="n">
-        <v>1000</v>
+        <v>56493213</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2858,11 +2858,11 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>4613</v>
+        <v>4614</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>OBRAS E INSTALAÇÕES</t>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
+          <t xml:space="preserve">INVESTIMENTOS PARTICIPAÇÕES SOCIETÁRIAS DA TRANSMISSÃO </t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
+          <t>TRANSMISSÃO DE ENERGIA ELÉTRICA</t>
         </is>
       </c>
     </row>
@@ -2920,20 +2920,20 @@
         <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>3007</v>
+        <v>3001</v>
       </c>
       <c r="N30" t="n">
-        <v>121588957</v>
+        <v>1000</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>4614</v>
+        <v>4613</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+          <t>OBRAS E INSTALAÇÕES</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
+          <t>EXPANSÃO DO SISTEMA DE GERAÇÃO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -3004,20 +3004,20 @@
         <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="N31" t="n">
-        <v>28627843</v>
+        <v>121588957</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
+          <t xml:space="preserve"> REFORMAS, MELHORIAS E AMPLIAÇÕES DE USINAS</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3088,20 +3088,20 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M32" t="n">
-        <v>3014</v>
+        <v>3008</v>
       </c>
       <c r="N32" t="n">
-        <v>1080197578</v>
+        <v>28627843</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
+          <t>MANUTENÇÃO DA INFRAESTRUTURA DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3145,18 +3145,18 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>5401</v>
+        <v>5391</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+          <t>CEMIG GERAÇÃO E TRANSMISSÃO S.A - CEMIG GERAÇÃO E TRANSMISSÃO</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3166,26 +3166,26 @@
         <v>752</v>
       </c>
       <c r="J33" t="n">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M33" t="n">
-        <v>3002</v>
+        <v>3014</v>
       </c>
       <c r="N33" t="n">
-        <v>5320034427</v>
+        <v>1080197578</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+          <t>INVESTIMENTOS EM PARTICIPAÇÕES SOCIETÁRIAS DA GERAÇÃO</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+          <t xml:space="preserve">GERAÇÃO DE ENERGIA ELÉTRICA </t>
         </is>
       </c>
     </row>
@@ -3256,20 +3256,20 @@
         <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="N34" t="n">
-        <v>250370467</v>
+        <v>5320034427</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3295,10 +3295,94 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t xml:space="preserve">EXECUÇÃO DO PLANO DE DESENVOLVIMENTO DA DISTRIBUIDORA (PDD) </t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1220</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONÔMICO - CEMIG DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5401</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CEMIG DISTRIBUIÇÃO S.A - CEMIG DISTRIBUIDORA</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" t="n">
+        <v>752</v>
+      </c>
+      <c r="J35" t="n">
+        <v>72</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3003</v>
+      </c>
+      <c r="N35" t="n">
+        <v>250370467</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
           <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>4610 - IMOBILIZAÇÕES</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>4614</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>MÁQUINAS, APARELHOS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>51000</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANUTENÇÃO DA INFRAESTRUTURA DA DISTRIBUIÇÃO </t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>DISTRIBUIÇÃO DE ENERGIA ELÉTRICA</t>
         </is>
